--- a/docs/testing/sprint-2-test-cases.xlsx
+++ b/docs/testing/sprint-2-test-cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a051af261022392/Documents/Personal Projects/GradNavi/docs/testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08_Personals\School Portfolio\GradNavi\docs\testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CE0AF99AD583CFB709907525EF79E0E0997F2BE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE728EA1-E17E-48CF-8E10-E745AF16BB1E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4227E4-B09E-4D5B-A830-BB415CE277D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="1332" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11820" yWindow="21480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="605">
   <si>
     <t>GradNavi Sprint 2 Test Dashboard</t>
   </si>
@@ -1330,9 +1330,6 @@
     <t>WBS 5.2 implementation is MD-owned. Repeat-import/idempotency verification was already executed by Jerald.</t>
   </si>
   <si>
-    <t>Not executed. This teammate/shared verification remains outside Jerald's remaining test scope unless the team reruns it.</t>
-  </si>
-  <si>
     <t>Automated test confirmed a full weighted Skill match returns 100.00.</t>
   </si>
   <si>
@@ -1456,30 +1453,12 @@
     <t>S2-READ-12 validation completed with PASS.</t>
   </si>
   <si>
-    <t>WBS 5.6 implementation is not integrated into feature/sprint-2; only the joyee/figma-ui-design-v2 design branch is present.</t>
-  </si>
-  <si>
-    <t>Keep Blocked until Joyee's WBS 5.6 implementation is integrated.</t>
-  </si>
-  <si>
     <t>WBS 5.7 exists on enamul/wbs-5.7-learning-roadmap-api but is not merged into feature/sprint-2.</t>
   </si>
   <si>
     <t>Keep Blocked until MD's WBS 5.7 branch is rebased/merged into the shared Sprint 2 branch.</t>
   </si>
   <si>
-    <t>WBS 5.8 implementation is not integrated; WBS 5.7 is also not merged into feature/sprint-2.</t>
-  </si>
-  <si>
-    <t>Keep Blocked until Joyee's WBS 5.8 and its WBS 5.7 backend dependency are integrated.</t>
-  </si>
-  <si>
-    <t>Full Sprint 2 gate is not satisfied: WBS 5.6, WBS 5.7 and WBS 5.8 are not integrated.</t>
-  </si>
-  <si>
-    <t>WBS 5.4 and 5.5 are present. End-to-end execution must wait for the remaining frontend/learning components.</t>
-  </si>
-  <si>
     <t>Full backend regression suite passed registration, login, JWT and authentication-route tests with no Sprint 1 authentication regression.</t>
   </si>
   <si>
@@ -1501,13 +1480,376 @@
     <t>Profile ownership tests passed; authenticated users did not receive another Student's protected profile-derived data.</t>
   </si>
   <si>
-    <t>The 185-test suite created test_gradnavi_db and applied migrations successfully, but a dedicated migration-drift check was not captured.</t>
-  </si>
-  <si>
-    <t>docs/testing/evidence/sprint-2/S2-EV-007A-full-backend-regression-start.png; docs/testing/evidence/sprint-2/S2-EV-007E-full-backend-regression-summary-pass.png</t>
-  </si>
-  <si>
-    <t>Supporting connectivity evidence exists, but keep Not Run because the full expected result includes migration drift verification.</t>
+    <t>Authenticated student Career Analysis flow was executed and shared Career/Skill reference counts remained unchanged: 36 active Careers, 2,873 Skills, 9,959 CareerSkill links, 10,038 CareerSkillEvidence rows.</t>
+  </si>
+  <si>
+    <t>S2-EV-017 / S2-EV-018 / S2-EV-019 / S2-EV-020 / S2-EV-021 / S2-EV-022</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-018A-desktop-recommendations-ranked-list-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-020A-desktop-skill-gap-readiness-selected-career-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-021A-desktop-roadmap-ordered-steps-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-022A-desktop-learning-resources-mapped-skill-1440x900.png</t>
+  </si>
+  <si>
+    <t>Executed through authenticated local Student flow. Dataset/reference rows were not modified; only controlled Student Profile rows were temporarily changed and restored for state tests.</t>
+  </si>
+  <si>
+    <t>Career Recommendations loaded from the authenticated API and displayed a ranked list with Software Engineer as rank 1 and six other matches.</t>
+  </si>
+  <si>
+    <t>S2-EV-017 / S2-EV-018 / S2-EV-019</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-018A-desktop-recommendations-ranked-list-1440x900.png</t>
+  </si>
+  <si>
+    <t>Executed in the local browser automation environment against local Vite and Django servers.</t>
+  </si>
+  <si>
+    <t>Frontend order matched API order for the first seven recommendations: Software Engineer, DevOps Engineer, Data Engineer, Data Scientist, Cloud Engineer, Data Analyst, Data Architect.</t>
+  </si>
+  <si>
+    <t>API rank-order check directly matched visible browser order.</t>
+  </si>
+  <si>
+    <t>Recommendation score, AI explanation area, strongest evidence, priority gap, and scoring weights were visible.</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-019A-desktop-scoring-explanation-details-1440x900.png</t>
+  </si>
+  <si>
+    <t>Expanded How scoring works and verified displayed weighting/factors.</t>
+  </si>
+  <si>
+    <t>Selecting View Skill Gaps for the top Software Engineer recommendation loaded selected-career Skill Gap Analysis with readiness details.</t>
+  </si>
+  <si>
+    <t>S2-EV-020</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-020A-desktop-skill-gap-readiness-selected-career-1440x900.png</t>
+  </si>
+  <si>
+    <t>Selection preserved career_id=3 from the recommendation action.</t>
+  </si>
+  <si>
+    <t>Career Match and Readiness appeared as separate metrics on recommendation cards and selected-career analysis.</t>
+  </si>
+  <si>
+    <t>S2-EV-017 / S2-EV-018 / S2-EV-019 / S2-EV-020</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-018A-desktop-recommendations-ranked-list-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-020A-desktop-skill-gap-readiness-selected-career-1440x900.png</t>
+  </si>
+  <si>
+    <t>Top Match showed Career Match 85% and Readiness 6%; Skill Gap Analysis showed separate Readiness Score.</t>
+  </si>
+  <si>
+    <t>Requirement Details distinguished Missing and Below Requirement statuses, including Critical Thinking as Below Requirement and multiple missing skills.</t>
+  </si>
+  <si>
+    <t>Requirement table showed status labels and current evidence values.</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-024A-full-empty-profile-recommendations-error-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-027-retest-profile-restoration.txt</t>
+  </si>
+  <si>
+    <t>DEF-S2-001</t>
+  </si>
+  <si>
+    <t>Health Information Manager selected-career Skill Gap Analysis displayed a controlled insufficient-evidence state with 0 requirements and no invented resources.</t>
+  </si>
+  <si>
+    <t>S2-EV-013</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-013A-s2-ui-08-insufficient-evidence-controlled.png</t>
+  </si>
+  <si>
+    <t>Used active Career ID 24, identified in the Sprint 2 plan as the insufficient-evidence case.</t>
+  </si>
+  <si>
+    <t>S2-EV-014</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-014A-s2-qual-02-keyboard-focus-navigation.png</t>
+  </si>
+  <si>
+    <t>Responsive viewport tooling unavailable in current browser automation provider.</t>
+  </si>
+  <si>
+    <t>Career Roadmap loaded for Software Engineer with an ordered 18-step plan.</t>
+  </si>
+  <si>
+    <t>S2-EV-021</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-021A-desktop-roadmap-ordered-steps-1440x900.png</t>
+  </si>
+  <si>
+    <t>Roadmap overview loaded from backend for career_id=3.</t>
+  </si>
+  <si>
+    <t>Roadmap displayed ordered step numbers beginning with Computers and Electronics, Judgment and Decision Making, and Mathematics Knowledge.</t>
+  </si>
+  <si>
+    <t>Visible order matched the backend roadmap priority order.</t>
+  </si>
+  <si>
+    <t>Roadmap skill names matched selected-career gaps shown in Skill Gap Analysis.</t>
+  </si>
+  <si>
+    <t>S2-EV-020 / S2-EV-021</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-020A-desktop-skill-gap-readiness-selected-career-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-021A-desktop-roadmap-ordered-steps-1440x900.png</t>
+  </si>
+  <si>
+    <t>Top roadmap priorities matched Fix First/Requirement Detail skills.</t>
+  </si>
+  <si>
+    <t>Learning Resources opened from a roadmap step and displayed resource cards mapped to Judgment and Decision Making.</t>
+  </si>
+  <si>
+    <t>S2-EV-022</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-022A-desktop-learning-resources-mapped-skill-1440x900.png</t>
+  </si>
+  <si>
+    <t>Resource cards included provider, type, checked date, and fit rationale.</t>
+  </si>
+  <si>
+    <t>Health Information Manager roadmap displayed a controlled empty state: 0 of 0 steps and No roadmap steps are available yet.</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-010B-s2-road-05-empty-roadmap-controlled.png</t>
+  </si>
+  <si>
+    <t>No false roadmap steps were displayed.</t>
+  </si>
+  <si>
+    <t>Invalid roadmap career_id displayed controlled error text: Selected career was not found, with retry/navigation actions.</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-010C-s2-road-06-roadmap-error-controlled.png</t>
+  </si>
+  <si>
+    <t>Used /career-roadmap?career_id=999999.</t>
+  </si>
+  <si>
+    <t>Navigation preserved selected Software Engineer context from recommendations to Skill Gap Analysis, Career Roadmap, and Learning Resources.</t>
+  </si>
+  <si>
+    <t>S2-EV-020 / S2-EV-021 / S2-EV-022</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-020A-desktop-skill-gap-readiness-selected-career-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-021A-desktop-roadmap-ordered-steps-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-022A-desktop-learning-resources-mapped-skill-1440x900.png</t>
+  </si>
+  <si>
+    <t>Context carried as career_id=3 across routes.</t>
+  </si>
+  <si>
+    <t>Partial-match Student completed the main Career Analysis flow: profile evidence, recommendations, explanation, selected career, skill gaps, readiness, roadmap, and learning resources.</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-017A-desktop-profile-baseline-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-018A-desktop-recommendations-ranked-list-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-020A-desktop-skill-gap-readiness-selected-career-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-021A-desktop-roadmap-ordered-steps-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-022A-desktop-learning-resources-mapped-skill-1440x900.png</t>
+  </si>
+  <si>
+    <t>Primary profile: IT/software-development synthetic baseline.</t>
+  </si>
+  <si>
+    <t>Controlled unrelated-skills browser scenario not completed in current run.</t>
+  </si>
+  <si>
+    <t>Insufficient-readiness/insufficient-evidence career remained controlled for Health Information Manager, with no false gaps or resources.</t>
+  </si>
+  <si>
+    <t>S2-EV-013 / S2-EV-021</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-013A-s2-ui-08-insufficient-evidence-controlled.png; docs/testing/evidence/sprint-2/S2-EV-010B-s2-road-05-empty-roadmap-controlled.png</t>
+  </si>
+  <si>
+    <t>Used active Career ID 24.</t>
+  </si>
+  <si>
+    <t>S2-EV-016</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-016-validation-lint-build-backend-tests.txt</t>
+  </si>
+  <si>
+    <t>Second synthetic Student browser credentials required for full E2E ownership-isolation execution.</t>
+  </si>
+  <si>
+    <t>Django system check passed, migration plan showed no unapplied migrations, and accounts/profiles/careers backend regression suite passed 623 tests.</t>
+  </si>
+  <si>
+    <t>This completes the previously missing dedicated migration-drift validation.</t>
+  </si>
+  <si>
+    <t>Representative authenticated non-AI API responses were observed under 2 seconds locally: recommendations 264.7 ms, readiness 91.2 ms, roadmap overview 132.9 ms, learning-resource recommendations 124.6 ms.</t>
+  </si>
+  <si>
+    <t>S2-EV-015</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-015-s2-qual-01-performance-observation.txt</t>
+  </si>
+  <si>
+    <t>Local classroom-use observation only; not production load testing.</t>
+  </si>
+  <si>
+    <t>Keyboard Tab traversal reached core navigation controls and maintained focusable route links.</t>
+  </si>
+  <si>
+    <t>Basic keyboard check only; not a full WCAG audit.</t>
+  </si>
+  <si>
+    <t>Representative responsive execution completed for Career Recommendations, Skill Gap/Readiness, and Career Roadmap at desktop 1440x900, tablet 1024x768, and mobile 390x844. No horizontal overflow was reported by the page checks.</t>
+  </si>
+  <si>
+    <t>S2-EV-025</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-025-desktop-recommendations-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-025-desktop-skill-gap-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-025-desktop-roadmap-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-025-tablet-recommendations-1024x768.png; docs/testing/evidence/sprint-2/S2-EV-025-tablet-skill-gap-1024x768.png; docs/testing/evidence/sprint-2/S2-EV-025-tablet-roadmap-1024x768.png; docs/testing/evidence/sprint-2/S2-EV-025-mobile-recommendations-390x844.png; docs/testing/evidence/sprint-2/S2-EV-025-mobile-skill-gap-390x844.png; docs/testing/evidence/sprint-2/S2-EV-025-mobile-roadmap-390x844.png</t>
+  </si>
+  <si>
+    <t>Representative widths used because Sprint 2 docs define categories but no fixed viewport matrix.</t>
+  </si>
+  <si>
+    <t>Chrome, Edge, and Firefox controllable browser sessions required.</t>
+  </si>
+  <si>
+    <t>New evidence files were created for executed in-scope rows, defects/blockers were recorded, and MD-owned rows were preserved.</t>
+  </si>
+  <si>
+    <t>S2-EV-017 / S2-EV-018 / S2-EV-019 to S2-EV-016</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-017A-desktop-profile-baseline-1440x900.png; docs/testing/evidence/sprint-2/S2-EV-016-validation-lint-build-backend-tests.txt</t>
+  </si>
+  <si>
+    <t>Evidence audit performed after workbook update.</t>
+  </si>
+  <si>
+    <t>Manual retest by Jerald on 20 September 2026 after DEF-S2-001 was fixed and merged into feature/sprint-3. With StudentSkill, StudentInterest, and CareerGoal records temporarily removed, Career Recommendations displayed controlled empty-profile guidance: "Complete your profile before generating career recommendations." The recommendations endpoint returned HTTP 400 instead of HTTP 500. No raw JSON parsing error or misleading scored recommendations were displayed.</t>
+  </si>
+  <si>
+    <t>S2-EV-029</t>
+  </si>
+  <si>
+    <t>Initial manual testing reproduced DEF-S2-001, where the fully empty profile caused HTTP 500 and exposed a raw JSON parsing error. After the defect fix was merged into feature/sprint-3, the official retest on jerald/sprint-2-integration-testing passed. The empty-profile state returned controlled guidance with HTTP 400. The test profile was restored and verified against the pre-test backup.</t>
+  </si>
+  <si>
+    <t>Official S2-UI-07 manual retest after DEF-S2-001 fix. Evidence covers empty-profile setup, empty Student Profile state, controlled Career Recommendations guidance with HTTP 400, and verified profile restoration.</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-029A-s2-ui-07-official-empty-profile-terminal.png; docs/testing/evidence/sprint-2/S2-EV-029B-s2-ui-07-official-empty-student-profile.png; docs/testing/evidence/sprint-2/S2-EV-029C-s2-ui-07-official-controlled-guidance-http-400.png; docs/testing/evidence/sprint-2/S2-EV-029D-s2-ui-07-official-profile-restoration-terminal.png</t>
+  </si>
+  <si>
+    <t>Official retest passed after DEF-S2-001 was fixed and merged into feature/sprint-3. Test profile restored to 6 skills, 4 interests, and 3 career goals with Software Engineer as the primary goal.</t>
+  </si>
+  <si>
+    <t>Manual retest by Jerald on 20 September 2026. Under Slow 4G network throttling, Career Recommendations displayed a controlled loading state with "Finding your career matches" and did not display stale recommendation results. With only /api/v1/recommendations/ blocked through Chrome Request conditions, the page remained on Career Recommendations and displayed "Recommendations unavailable" with "Failed to fetch". No false or stale recommendation data was shown. After disabling the request condition, Career Recommendations recovered normally and the recommendations endpoint returned HTTP 200.</t>
+  </si>
+  <si>
+    <t>S2-EV-030</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-030A-s2-ui-09-controlled-loading-state.png; docs/testing/evidence/sprint-2/S2-EV-030B-s2-ui-09-controlled-api-error-state.png; docs/testing/evidence/sprint-2/S2-EV-030C-s2-ui-09-recovery-normal-recommendations.png</t>
+  </si>
+  <si>
+    <t>Manual retest completed on jerald/sprint-2-integration-testing. Loading, isolated recommendation API failure, and recovery states were verified manually. No stale or false recommendation data was displayed during loading or API failure. Normal recommendations recovered after the request condition was disabled.</t>
+  </si>
+  <si>
+    <t>Manual S2-UI-09 retest covering controlled loading state, isolated Career Recommendations API failure, and successful recovery.</t>
+  </si>
+  <si>
+    <t>Loading state tested with Slow 4G throttling. API failure tested by blocking only /api/v1/recommendations/ through Chrome Request conditions. Recovery verified after disabling the condition with recommendations returning HTTP 200.</t>
+  </si>
+  <si>
+    <t>S2-EV-031</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-031A-s2-e2e-03-empty-studentskill-terminal.png; docs/testing/evidence/sprint-2/S2-EV-031B-s2-e2e-03-empty-skills-profile.png; docs/testing/evidence/sprint-2/S2-EV-031C-s2-e2e-03-career-recommendations-misleading-score.png; docs/testing/evidence/sprint-2/S2-EV-031D-s2-e2e-03-downstream-skill-gap-insufficient-profile.png; docs/testing/evidence/sprint-2/S2-EV-031E-s2-e2e-03-profile-restoration-terminal.png</t>
+  </si>
+  <si>
+    <t>Official S2-E2E-03 manual retest covering zero StudentSkill setup, profile verification, misleading scored Career Recommendation result, downstream Insufficient Profile result, and verified profile restoration.</t>
+  </si>
+  <si>
+    <t>DEF-S2-002. Zero StudentSkill profile received a 100% Career Match with no matched evidence. Downstream Skill Gap Analysis reported 0% readiness and Insufficient Profile. Profile restored after execution.</t>
+  </si>
+  <si>
+    <t>Manual retest by Jerald on 20 September 2026. Responsive behaviour was verified across desktop 1440x900, tablet 1024x768, and mobile 390x844. An initial mobile navigation and tablet Top Match layout issue was identified as DEF-S2-003 and fixed. After the fix was merged into feature/sprint-3 and brought into the Sprint 2 testing branch, the tablet Top Match layout stacked correctly, mobile navigation used an accessible burger drawer, Career Match and Readiness remained balanced, and Skill Gap Analysis and Career Roadmap remained usable without horizontal overflow. Keyboard testing verified visible focus, forward Tab navigation, backward Shift+Tab navigation, Enter activation, and keyboard navigation through the core flow.</t>
+  </si>
+  <si>
+    <t>S2-EV-032</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-032D-s2-ui-10-tablet-career-recommendations-fixed-1024x768.png; docs/testing/evidence/sprint-2/S2-EV-032G-s2-ui-10-mobile-career-recommendations-fixed-390x844.png; docs/testing/evidence/sprint-2/S2-EV-032H-s2-ui-10-mobile-navigation-drawer-390x844.png; docs/testing/evidence/sprint-2/S2-EV-032I-s2-ui-10-mobile-skill-gap-390x844.png; docs/testing/evidence/sprint-2/S2-EV-032J-s2-ui-10-mobile-roadmap-390x844.png; docs/testing/evidence/sprint-2/S2-EV-032K-s2-ui-10-keyboard-visible-focus.png</t>
+  </si>
+  <si>
+    <t>DEF-S2-003</t>
+  </si>
+  <si>
+    <t>Initial responsive defect found during manual S2-UI-10 execution. DEF-S2-003 was fixed and merged into feature/sprint-3. Official retest passed after verifying desktop, tablet, mobile, burger navigation, visible keyboard focus, Tab, Shift+Tab, Enter activation, and keyboard-accessible core navigation. Shift+Tab behaviour was manually verified and does not require a separate screenshot.</t>
+  </si>
+  <si>
+    <t>Manual end-to-end retest by Jerald on 20 September 2026. The unrelated-Skills scenario used three approved accounting Skills at Advanced proficiency with Career Goals temporarily removed to isolate Skill-based recommendation behaviour. Accountant (General), Taxation Accountant, and Management Accountant ranked first, second, and third. Software Engineer ranked 16 with an 18.61% Career Match, 0.00 competency score, no matched competencies, and no matched technologies. Software Engineer downstream readiness was 0%, with 0 matched, 0 partially matched, and 18 missing requirements. Learning Resources and Career Roadmap preserved the Software Engineer context and showed controlled missing-gap states without false evidence. The original test profile was restored successfully after execution.</t>
+  </si>
+  <si>
+    <t>S2-EV-033</t>
+  </si>
+  <si>
+    <t>Official S2-E2E-02 retest passed. Initial diagnostic execution retained existing Career Goals and showed that goal-based semantic context influenced ranking. The official isolated execution temporarily removed Career Goals while retaining three real accounting Skills and four Interests. Accounting careers ranked highest, while unrelated Software Engineer dropped to rank 16 with an 18.61% match and no matched competency or technology evidence. Downstream Skill Gap, Learning Resources, and Career Roadmap remained controlled. Original profile restoration passed.</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-033E-s2-e2e-02-unrelated-skills-no-career-goals-terminal.png; docs/testing/evidence/sprint-2/S2-EV-033F-s2-e2e-02-isolated-career-recommendations-top-match.png; docs/testing/evidence/sprint-2/S2-EV-033G-s2-e2e-02-isolated-other-career-matches.png; docs/testing/evidence/sprint-2/S2-EV-033H-s2-e2e-02-software-engineer-low-match-snapshot-terminal.txt; docs/testing/evidence/sprint-2/S2-EV-033I-s2-e2e-02-software-engineer-skill-gap.png; docs/testing/evidence/sprint-2/S2-EV-033J-s2-e2e-02-software-engineer-gap-details.png; docs/testing/evidence/sprint-2/S2-EV-033K-s2-e2e-02-software-engineer-learning-resources.png; docs/testing/evidence/sprint-2/S2-EV-033L-s2-e2e-02-software-engineer-roadmap.png; docs/testing/evidence/sprint-2/S2-EV-033M-s2-e2e-02-profile-restoration-terminal.png</t>
+  </si>
+  <si>
+    <t>Official unrelated-Skills end-to-end retest covering isolated profile state, recommendation ranking, Software Engineer low-match verification, Skill Gap, Learning Resources, Career Roadmap, and profile restoration.</t>
+  </si>
+  <si>
+    <t>No false Software Engineer match observed. Software Engineer ranked 16 at 18.61%, with 0.00 competency score and no matched competencies or technologies. Downstream readiness was 0% with 18 missing requirements. Original profile restored successfully.</t>
+  </si>
+  <si>
+    <t>Retested after DEF-S2-005. With StudentSkill reduced to 0 while 4 Interests and 3 Career Goals remained, Career Recommendations returned the controlled incomplete-profile state instead of ranked Career matches. The recommendation endpoint returned insufficient_profile_context and no misleading recommendation scores were shown. The original profile was restored to 6 Skills, 4 Interests, and 3 Career Goals after testing.</t>
+  </si>
+  <si>
+    <t>DEF-S2-005</t>
+  </si>
+  <si>
+    <t>S2-EV-035</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-035A-s2-e2e-03-empty-skills-profile.png; docs/testing/evidence/sprint-2/S2-EV-035B-s2-e2e-03-career-recommendations-fail.png; docs/testing/evidence/sprint-2/S2-EV-035C-s2-e2e-03-post-fix-controlled-recommendations.png</t>
+  </si>
+  <si>
+    <t>Initial retest failed because ranked recommendations were still generated with zero Skills. DEF-S2-005 added an empty-Skills recommendation guard before cache lookup and composite scoring. The post-fix browser retest passed.</t>
+  </si>
+  <si>
+    <t>S2-EV-036</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-036A-s2-e2e-05-student-ownership-isolation-terminal.png</t>
+  </si>
+  <si>
+    <t>Student ownership isolation passed. Student B remained isolated from Student A profile and derived readiness data even when Student A's profile ID was supplied. Student B returned 0 Skills, 0 Interests, and 0 Career Goals. Student A readiness returned scored with 5.54, while Student B returned insufficient_profile with no readiness score. Temporary Student B was deleted after testing.</t>
+  </si>
+  <si>
+    <t>Previously blocked ownership test completed successfully. Profile and derived Career readiness data remained scoped to the authenticated Student.</t>
+  </si>
+  <si>
+    <t>ID: S2-EV-037</t>
+  </si>
+  <si>
+    <t>Manual cross-browser verification by Jerald on 20 September 2026.</t>
+  </si>
+  <si>
+    <t>Manual cross-browser verification passed in Google Chrome, Microsoft Edge, and Mozilla Firefox. Login, Career Recommendations, Skill Gap Analysis, Learning Resources, Career Roadmap, navigation, and logout worked without blocking browser-specific errors.</t>
+  </si>
+  <si>
+    <t>Chrome: Pass. Edge: Pass. Firefox: Pass.</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +2054,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1834,6 +2176,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1846,18 +2207,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{03CE8168-D44C-42ED-BFF2-EB81F1D2AF07}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1905,6 +2260,33 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1932,15 +2314,15 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Steps"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Expected Result"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Test Owner"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Status"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Actual Result"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tester"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidence ID"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidence Reference"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Blocked Dependency"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Defect Reference"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Automation"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Notes"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Status" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Actual Result" dataDxfId="12" dataCellStyle="Normal 2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tester" dataDxfId="11" dataCellStyle="Normal 2"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidence ID" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidence Reference" dataDxfId="9" dataCellStyle="Normal 2"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Blocked Dependency" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Defect Reference" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Automation" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Notes" dataDxfId="5" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2142,7 +2524,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2155,16 +2537,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.35" customHeight="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7"/>
@@ -2176,7 +2558,7 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2198,7 +2580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="15">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -2223,13 +2605,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="10">
         <f>COUNTIF('Test Cases'!L2:L81,"Pass")</f>
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="11" t="s">
@@ -2248,7 +2630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" ht="15">
       <c r="A6" s="9" t="s">
         <v>11</v>
       </c>
@@ -2273,13 +2655,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="15">
       <c r="A7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="10">
         <f>COUNTIF('Test Cases'!L2:L81,"Blocked")</f>
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
@@ -2298,7 +2680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" ht="15">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
@@ -2318,13 +2700,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" ht="15">
       <c r="A9" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="14">
         <f>COUNTIF('Test Cases'!L2:L81,"Not Run")</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -2343,19 +2725,19 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" ht="15.6">
-      <c r="A11" s="42" t="s">
+    <row r="11" spans="1:8" ht="15.75">
+      <c r="A11" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+    </row>
+    <row r="12" spans="1:8" ht="15">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -2373,7 +2755,7 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" ht="27.6">
+    <row r="13" spans="1:8" ht="28.5">
       <c r="A13" s="16" t="s">
         <v>24</v>
       </c>
@@ -2391,7 +2773,7 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" ht="27.6">
+    <row r="14" spans="1:8" ht="28.5">
       <c r="A14" s="16" t="s">
         <v>27</v>
       </c>
@@ -2409,7 +2791,7 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" ht="27.6">
+    <row r="15" spans="1:8" ht="28.5">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2427,7 +2809,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" ht="27.6">
+    <row r="16" spans="1:8" ht="28.5">
       <c r="A16" s="16" t="s">
         <v>31</v>
       </c>
@@ -2445,7 +2827,7 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="27.6">
+    <row r="17" spans="1:8" ht="28.5">
       <c r="A17" s="21" t="s">
         <v>32</v>
       </c>
@@ -2473,19 +2855,19 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="43" t="s">
+    <row r="19" spans="1:8" ht="15">
+      <c r="A19" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-    </row>
-    <row r="20" spans="1:8" ht="55.2">
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+    </row>
+    <row r="20" spans="1:8" ht="57">
       <c r="A20" s="25" t="s">
         <v>36</v>
       </c>
@@ -2499,7 +2881,7 @@
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
     </row>
-    <row r="21" spans="1:8" ht="69">
+    <row r="21" spans="1:8" ht="71.25">
       <c r="A21" s="25" t="s">
         <v>38</v>
       </c>
@@ -2513,7 +2895,7 @@
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
     </row>
-    <row r="22" spans="1:8" ht="55.2">
+    <row r="22" spans="1:8" ht="57">
       <c r="A22" s="25" t="s">
         <v>40</v>
       </c>
@@ -2527,7 +2909,7 @@
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
     </row>
-    <row r="23" spans="1:8" ht="82.8">
+    <row r="23" spans="1:8" ht="85.5">
       <c r="A23" s="25" t="s">
         <v>42</v>
       </c>
@@ -2541,7 +2923,7 @@
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
     </row>
-    <row r="24" spans="1:8" ht="69">
+    <row r="24" spans="1:8" ht="71.25">
       <c r="A24" s="25" t="s">
         <v>44</v>
       </c>
@@ -2568,7 +2950,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T81"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2591,7 +2973,7 @@
     <col min="20" max="20" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="28.8" customHeight="1">
+    <row r="1" spans="1:20" ht="28.9" customHeight="1">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -2622,38 +3004,38 @@
       <c r="J1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="45" t="s">
+      <c r="K1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="45" t="s">
+      <c r="L1" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="45" t="s">
+      <c r="O1" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="45" t="s">
+      <c r="P1" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="45" t="s">
+      <c r="Q1" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="45" t="s">
+      <c r="R1" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="45" t="s">
+      <c r="S1" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="45" t="s">
+      <c r="T1" s="41" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="55.2">
+    <row r="2" spans="1:20" ht="57">
       <c r="A2" s="28" t="s">
         <v>64</v>
       </c>
@@ -2684,34 +3066,34 @@
       <c r="J2" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="46" t="s">
+      <c r="K2" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="46" t="s">
+      <c r="M2" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="N2" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O2" s="46" t="s">
+      <c r="N2" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="42" t="s">
         <v>408</v>
       </c>
-      <c r="P2" s="46" t="s">
+      <c r="P2" s="42" t="s">
         <v>409</v>
       </c>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46" t="s">
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T2" s="46" t="s">
+      <c r="T2" s="42" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="41.4">
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="28" t="s">
         <v>74</v>
       </c>
@@ -2742,34 +3124,34 @@
       <c r="J3" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="K3" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="46" t="s">
+      <c r="K3" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="46" t="s">
+      <c r="M3" s="42" t="s">
         <v>411</v>
       </c>
-      <c r="N3" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O3" s="46" t="s">
+      <c r="N3" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="42" t="s">
         <v>408</v>
       </c>
-      <c r="P3" s="46" t="s">
+      <c r="P3" s="42" t="s">
         <v>409</v>
       </c>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46" t="s">
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="T3" s="42" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="82.8">
+    <row r="4" spans="1:20" ht="85.5">
       <c r="A4" s="28" t="s">
         <v>78</v>
       </c>
@@ -2800,34 +3182,34 @@
       <c r="J4" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" s="46" t="s">
+      <c r="K4" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="46" t="s">
+      <c r="M4" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="N4" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O4" s="46" t="s">
+      <c r="N4" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P4" s="46" t="s">
+      <c r="P4" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46" t="s">
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T4" s="46" t="s">
+      <c r="T4" s="42" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="82.8">
+    <row r="5" spans="1:20" ht="85.5">
       <c r="A5" s="28" t="s">
         <v>84</v>
       </c>
@@ -2858,34 +3240,34 @@
       <c r="J5" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="46" t="s">
+      <c r="K5" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="46" t="s">
+      <c r="M5" s="42" t="s">
         <v>417</v>
       </c>
-      <c r="N5" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O5" s="46" t="s">
+      <c r="N5" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P5" s="46" t="s">
+      <c r="P5" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46" t="s">
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T5" s="46" t="s">
+      <c r="T5" s="42" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="82.8">
+    <row r="6" spans="1:20" ht="85.5">
       <c r="A6" s="28" t="s">
         <v>90</v>
       </c>
@@ -2916,34 +3298,34 @@
       <c r="J6" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="K6" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="46" t="s">
+      <c r="K6" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M6" s="46" t="s">
+      <c r="M6" s="42" t="s">
         <v>421</v>
       </c>
-      <c r="N6" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O6" s="46" t="s">
+      <c r="N6" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P6" s="46" t="s">
+      <c r="P6" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46" t="s">
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T6" s="46" t="s">
+      <c r="T6" s="42" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="82.8">
+    <row r="7" spans="1:20" ht="85.5">
       <c r="A7" s="28" t="s">
         <v>96</v>
       </c>
@@ -2974,34 +3356,34 @@
       <c r="J7" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="K7" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7" s="46" t="s">
+      <c r="K7" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="46" t="s">
+      <c r="M7" s="42" t="s">
         <v>423</v>
       </c>
-      <c r="N7" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O7" s="46" t="s">
+      <c r="N7" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="42" t="s">
         <v>424</v>
       </c>
-      <c r="P7" s="46" t="s">
+      <c r="P7" s="42" t="s">
         <v>425</v>
       </c>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46" t="s">
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T7" s="46" t="s">
+      <c r="T7" s="42" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="82.8">
+    <row r="8" spans="1:20" ht="85.5">
       <c r="A8" s="28" t="s">
         <v>101</v>
       </c>
@@ -3032,34 +3414,34 @@
       <c r="J8" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="K8" s="46" t="s">
+      <c r="K8" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="46" t="s">
+      <c r="L8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="46" t="s">
+      <c r="M8" s="42" t="s">
         <v>427</v>
       </c>
-      <c r="N8" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O8" s="46" t="s">
+      <c r="N8" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8" s="42" t="s">
         <v>428</v>
       </c>
-      <c r="P8" s="46" t="s">
+      <c r="P8" s="42" t="s">
         <v>429</v>
       </c>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46" t="s">
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T8" s="46" t="s">
+      <c r="T8" s="42" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="55.2">
+    <row r="9" spans="1:20" ht="213.75">
       <c r="A9" s="28" t="s">
         <v>109</v>
       </c>
@@ -3090,26 +3472,34 @@
       <c r="J9" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46" t="s">
+      <c r="L9" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="N9" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="P9" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="T9" s="46" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="82.8">
+      <c r="T9" s="42" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="85.5">
       <c r="A10" s="28" t="s">
         <v>117</v>
       </c>
@@ -3140,34 +3530,34 @@
       <c r="J10" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="K10" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L10" s="46" t="s">
+      <c r="K10" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="46" t="s">
+      <c r="M10" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="N10" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O10" s="42" t="s">
+        <v>414</v>
+      </c>
+      <c r="P10" s="42" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T10" s="42" t="s">
         <v>432</v>
       </c>
-      <c r="N10" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>414</v>
-      </c>
-      <c r="P10" s="46" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T10" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="82.8">
+    </row>
+    <row r="11" spans="1:20" ht="85.5">
       <c r="A11" s="28" t="s">
         <v>126</v>
       </c>
@@ -3198,34 +3588,34 @@
       <c r="J11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="K11" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L11" s="46" t="s">
+      <c r="K11" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="46" t="s">
-        <v>434</v>
-      </c>
-      <c r="N11" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11" s="46" t="s">
+      <c r="M11" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="N11" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P11" s="46" t="s">
+      <c r="P11" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46" t="s">
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T11" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="82.8">
+      <c r="T11" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="85.5">
       <c r="A12" s="28" t="s">
         <v>129</v>
       </c>
@@ -3256,34 +3646,34 @@
       <c r="J12" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="K12" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L12" s="46" t="s">
+      <c r="K12" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="46" t="s">
-        <v>435</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O12" s="46" t="s">
+      <c r="M12" s="42" t="s">
+        <v>434</v>
+      </c>
+      <c r="N12" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O12" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P12" s="46" t="s">
+      <c r="P12" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="46" t="s">
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T12" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="82.8">
+      <c r="T12" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="85.5">
       <c r="A13" s="28" t="s">
         <v>132</v>
       </c>
@@ -3314,34 +3704,34 @@
       <c r="J13" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="K13" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L13" s="46" t="s">
+      <c r="K13" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="46" t="s">
-        <v>436</v>
-      </c>
-      <c r="N13" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O13" s="46" t="s">
+      <c r="M13" s="42" t="s">
+        <v>435</v>
+      </c>
+      <c r="N13" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P13" s="46" t="s">
+      <c r="P13" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46" t="s">
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="82.8">
+      <c r="T13" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="85.5">
       <c r="A14" s="28" t="s">
         <v>135</v>
       </c>
@@ -3372,34 +3762,34 @@
       <c r="J14" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="K14" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L14" s="46" t="s">
+      <c r="K14" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="N14" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O14" s="46" t="s">
+      <c r="M14" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="N14" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O14" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P14" s="46" t="s">
+      <c r="P14" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46" t="s">
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T14" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="82.8">
+      <c r="T14" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="85.5">
       <c r="A15" s="28" t="s">
         <v>138</v>
       </c>
@@ -3430,34 +3820,34 @@
       <c r="J15" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="K15" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L15" s="46" t="s">
+      <c r="K15" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="46" t="s">
-        <v>438</v>
-      </c>
-      <c r="N15" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O15" s="46" t="s">
+      <c r="M15" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="N15" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O15" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P15" s="46" t="s">
+      <c r="P15" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46" t="s">
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T15" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="82.8">
+      <c r="T15" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="85.5">
       <c r="A16" s="28" t="s">
         <v>141</v>
       </c>
@@ -3488,34 +3878,34 @@
       <c r="J16" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="K16" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L16" s="46" t="s">
+      <c r="K16" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="46" t="s">
-        <v>439</v>
-      </c>
-      <c r="N16" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O16" s="46" t="s">
+      <c r="M16" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="N16" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O16" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P16" s="46" t="s">
+      <c r="P16" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46" t="s">
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="82.8">
+      <c r="T16" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="85.5">
       <c r="A17" s="28" t="s">
         <v>144</v>
       </c>
@@ -3546,34 +3936,34 @@
       <c r="J17" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="K17" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L17" s="46" t="s">
+      <c r="K17" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="46" t="s">
-        <v>440</v>
-      </c>
-      <c r="N17" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O17" s="46" t="s">
+      <c r="M17" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="N17" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P17" s="46" t="s">
+      <c r="P17" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46" t="s">
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T17" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="82.8">
+      <c r="T17" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="85.5">
       <c r="A18" s="28" t="s">
         <v>147</v>
       </c>
@@ -3604,34 +3994,34 @@
       <c r="J18" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="K18" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L18" s="46" t="s">
+      <c r="K18" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="46" t="s">
-        <v>441</v>
-      </c>
-      <c r="N18" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O18" s="46" t="s">
+      <c r="M18" s="42" t="s">
+        <v>440</v>
+      </c>
+      <c r="N18" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O18" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P18" s="46" t="s">
+      <c r="P18" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="46"/>
-      <c r="S18" s="46" t="s">
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T18" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="82.8">
+      <c r="T18" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="85.5">
       <c r="A19" s="28" t="s">
         <v>150</v>
       </c>
@@ -3662,34 +4052,34 @@
       <c r="J19" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="K19" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L19" s="46" t="s">
+      <c r="K19" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M19" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="N19" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O19" s="46" t="s">
+      <c r="M19" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="N19" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O19" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="P19" s="46" t="s">
+      <c r="P19" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46" t="s">
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T19" s="46" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="82.8">
+      <c r="T19" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="85.5">
       <c r="A20" s="28" t="s">
         <v>153</v>
       </c>
@@ -3720,34 +4110,34 @@
       <c r="J20" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="46" t="s">
+      <c r="K20" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="46" t="s">
+      <c r="L20" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="46" t="s">
+      <c r="M20" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="N20" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O20" s="42" t="s">
         <v>443</v>
       </c>
-      <c r="N20" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O20" s="46" t="s">
+      <c r="P20" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P20" s="46" t="s">
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T20" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T20" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="82.8">
+    </row>
+    <row r="21" spans="1:20" ht="85.5">
       <c r="A21" s="28" t="s">
         <v>162</v>
       </c>
@@ -3778,34 +4168,34 @@
       <c r="J21" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="K21" s="46" t="s">
+      <c r="K21" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L21" s="46" t="s">
+      <c r="L21" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="46" t="s">
-        <v>447</v>
-      </c>
-      <c r="N21" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O21" s="46" t="s">
+      <c r="M21" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="N21" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O21" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P21" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P21" s="46" t="s">
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T21" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T21" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="82.8">
+    </row>
+    <row r="22" spans="1:20" ht="85.5">
       <c r="A22" s="28" t="s">
         <v>165</v>
       </c>
@@ -3836,34 +4226,34 @@
       <c r="J22" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="46" t="s">
+      <c r="L22" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="46" t="s">
-        <v>448</v>
-      </c>
-      <c r="N22" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O22" s="46" t="s">
+      <c r="M22" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="N22" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O22" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P22" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P22" s="46" t="s">
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T22" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T22" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="82.8">
+    </row>
+    <row r="23" spans="1:20" ht="85.5">
       <c r="A23" s="28" t="s">
         <v>168</v>
       </c>
@@ -3894,34 +4284,34 @@
       <c r="J23" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="K23" s="46" t="s">
+      <c r="K23" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="46" t="s">
+      <c r="L23" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="46" t="s">
-        <v>449</v>
-      </c>
-      <c r="N23" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O23" s="46" t="s">
+      <c r="M23" s="42" t="s">
+        <v>448</v>
+      </c>
+      <c r="N23" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O23" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P23" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P23" s="46" t="s">
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T23" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q23" s="46"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T23" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="82.8">
+    </row>
+    <row r="24" spans="1:20" ht="85.5">
       <c r="A24" s="28" t="s">
         <v>171</v>
       </c>
@@ -3952,34 +4342,34 @@
       <c r="J24" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="K24" s="46" t="s">
+      <c r="K24" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L24" s="46" t="s">
+      <c r="L24" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="46" t="s">
-        <v>450</v>
-      </c>
-      <c r="N24" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O24" s="46" t="s">
+      <c r="M24" s="42" t="s">
+        <v>449</v>
+      </c>
+      <c r="N24" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O24" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P24" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P24" s="46" t="s">
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T24" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T24" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="82.8">
+    </row>
+    <row r="25" spans="1:20" ht="85.5">
       <c r="A25" s="28" t="s">
         <v>174</v>
       </c>
@@ -4010,34 +4400,34 @@
       <c r="J25" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="K25" s="46" t="s">
+      <c r="K25" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="46" t="s">
+      <c r="L25" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M25" s="46" t="s">
-        <v>451</v>
-      </c>
-      <c r="N25" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O25" s="46" t="s">
+      <c r="M25" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="N25" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O25" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P25" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P25" s="46" t="s">
+      <c r="Q25" s="42"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T25" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46"/>
-      <c r="S25" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T25" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="82.8">
+    </row>
+    <row r="26" spans="1:20" ht="85.5">
       <c r="A26" s="28" t="s">
         <v>177</v>
       </c>
@@ -4068,34 +4458,34 @@
       <c r="J26" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="K26" s="46" t="s">
+      <c r="K26" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="46" t="s">
+      <c r="L26" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="46" t="s">
-        <v>452</v>
-      </c>
-      <c r="N26" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O26" s="46" t="s">
+      <c r="M26" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="N26" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O26" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P26" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P26" s="46" t="s">
+      <c r="Q26" s="42"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T26" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T26" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="82.8">
+    </row>
+    <row r="27" spans="1:20" ht="85.5">
       <c r="A27" s="28" t="s">
         <v>179</v>
       </c>
@@ -4126,34 +4516,34 @@
       <c r="J27" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="K27" s="46" t="s">
+      <c r="K27" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L27" s="46" t="s">
+      <c r="L27" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="46" t="s">
+      <c r="M27" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="N27" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O27" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P27" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T27" s="42" t="s">
         <v>453</v>
       </c>
-      <c r="N27" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O27" s="46" t="s">
-        <v>444</v>
-      </c>
-      <c r="P27" s="46" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T27" s="46" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="82.8">
+    </row>
+    <row r="28" spans="1:20" ht="85.5">
       <c r="A28" s="28" t="s">
         <v>182</v>
       </c>
@@ -4184,34 +4574,34 @@
       <c r="J28" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="K28" s="46" t="s">
+      <c r="K28" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L28" s="46" t="s">
+      <c r="L28" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M28" s="46" t="s">
-        <v>455</v>
-      </c>
-      <c r="N28" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O28" s="46" t="s">
+      <c r="M28" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="N28" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O28" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P28" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P28" s="46" t="s">
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T28" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T28" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="82.8">
+    </row>
+    <row r="29" spans="1:20" ht="85.5">
       <c r="A29" s="28" t="s">
         <v>185</v>
       </c>
@@ -4242,34 +4632,34 @@
       <c r="J29" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="K29" s="46" t="s">
+      <c r="K29" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="46" t="s">
+      <c r="L29" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="46" t="s">
-        <v>456</v>
-      </c>
-      <c r="N29" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O29" s="46" t="s">
+      <c r="M29" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="N29" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O29" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="P29" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="P29" s="46" t="s">
+      <c r="Q29" s="42"/>
+      <c r="R29" s="42"/>
+      <c r="S29" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="T29" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="46"/>
-      <c r="S29" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="T29" s="46" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="82.8">
+    </row>
+    <row r="30" spans="1:20" ht="85.5">
       <c r="A30" s="28" t="s">
         <v>188</v>
       </c>
@@ -4300,34 +4690,34 @@
       <c r="J30" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="K30" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L30" s="46" t="s">
+      <c r="K30" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L30" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M30" s="46" t="s">
+      <c r="M30" s="42" t="s">
+        <v>456</v>
+      </c>
+      <c r="N30" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O30" s="42" t="s">
+        <v>418</v>
+      </c>
+      <c r="P30" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="42"/>
+      <c r="S30" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="T30" s="42" t="s">
         <v>457</v>
       </c>
-      <c r="N30" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O30" s="46" t="s">
-        <v>418</v>
-      </c>
-      <c r="P30" s="46" t="s">
-        <v>419</v>
-      </c>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="T30" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="82.8">
+    </row>
+    <row r="31" spans="1:20" ht="85.5">
       <c r="A31" s="28" t="s">
         <v>197</v>
       </c>
@@ -4358,34 +4748,34 @@
       <c r="J31" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="K31" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L31" s="46" t="s">
+      <c r="K31" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L31" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M31" s="46" t="s">
-        <v>459</v>
-      </c>
-      <c r="N31" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O31" s="46" t="s">
+      <c r="M31" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="N31" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O31" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P31" s="46" t="s">
+      <c r="P31" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q31" s="46"/>
-      <c r="R31" s="46"/>
-      <c r="S31" s="46" t="s">
+      <c r="Q31" s="42"/>
+      <c r="R31" s="42"/>
+      <c r="S31" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T31" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="82.8">
+      <c r="T31" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="85.5">
       <c r="A32" s="28" t="s">
         <v>200</v>
       </c>
@@ -4416,34 +4806,34 @@
       <c r="J32" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="K32" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L32" s="46" t="s">
+      <c r="K32" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L32" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="46" t="s">
-        <v>460</v>
-      </c>
-      <c r="N32" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O32" s="46" t="s">
+      <c r="M32" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="N32" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O32" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P32" s="46" t="s">
+      <c r="P32" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q32" s="46"/>
-      <c r="R32" s="46"/>
-      <c r="S32" s="46" t="s">
+      <c r="Q32" s="42"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T32" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="82.8">
+      <c r="T32" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="85.5">
       <c r="A33" s="28" t="s">
         <v>203</v>
       </c>
@@ -4474,34 +4864,34 @@
       <c r="J33" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="K33" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L33" s="46" t="s">
+      <c r="K33" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L33" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="46" t="s">
-        <v>461</v>
-      </c>
-      <c r="N33" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O33" s="46" t="s">
+      <c r="M33" s="42" t="s">
+        <v>460</v>
+      </c>
+      <c r="N33" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O33" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P33" s="46" t="s">
+      <c r="P33" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="46"/>
-      <c r="S33" s="46" t="s">
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T33" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" ht="82.8">
+      <c r="T33" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="85.5">
       <c r="A34" s="28" t="s">
         <v>206</v>
       </c>
@@ -4532,34 +4922,34 @@
       <c r="J34" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="K34" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L34" s="46" t="s">
+      <c r="K34" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L34" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M34" s="46" t="s">
-        <v>462</v>
-      </c>
-      <c r="N34" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O34" s="46" t="s">
+      <c r="M34" s="42" t="s">
+        <v>461</v>
+      </c>
+      <c r="N34" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O34" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P34" s="46" t="s">
+      <c r="P34" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q34" s="46"/>
-      <c r="R34" s="46"/>
-      <c r="S34" s="46" t="s">
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T34" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="82.8">
+      <c r="T34" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="85.5">
       <c r="A35" s="28" t="s">
         <v>209</v>
       </c>
@@ -4590,34 +4980,34 @@
       <c r="J35" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="K35" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L35" s="46" t="s">
+      <c r="K35" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L35" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="46" t="s">
-        <v>463</v>
-      </c>
-      <c r="N35" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O35" s="46" t="s">
+      <c r="M35" s="42" t="s">
+        <v>462</v>
+      </c>
+      <c r="N35" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O35" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P35" s="46" t="s">
+      <c r="P35" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46" t="s">
+      <c r="Q35" s="42"/>
+      <c r="R35" s="42"/>
+      <c r="S35" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T35" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="82.8">
+      <c r="T35" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="85.5">
       <c r="A36" s="28" t="s">
         <v>212</v>
       </c>
@@ -4648,34 +5038,34 @@
       <c r="J36" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="K36" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L36" s="46" t="s">
+      <c r="K36" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L36" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M36" s="46" t="s">
-        <v>464</v>
-      </c>
-      <c r="N36" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O36" s="46" t="s">
+      <c r="M36" s="42" t="s">
+        <v>463</v>
+      </c>
+      <c r="N36" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O36" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P36" s="46" t="s">
+      <c r="P36" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q36" s="46"/>
-      <c r="R36" s="46"/>
-      <c r="S36" s="46" t="s">
+      <c r="Q36" s="42"/>
+      <c r="R36" s="42"/>
+      <c r="S36" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T36" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="82.8">
+      <c r="T36" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="85.5">
       <c r="A37" s="28" t="s">
         <v>215</v>
       </c>
@@ -4706,34 +5096,34 @@
       <c r="J37" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="K37" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L37" s="46" t="s">
+      <c r="K37" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L37" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M37" s="46" t="s">
-        <v>465</v>
-      </c>
-      <c r="N37" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O37" s="46" t="s">
+      <c r="M37" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="N37" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O37" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P37" s="46" t="s">
+      <c r="P37" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46" t="s">
+      <c r="Q37" s="42"/>
+      <c r="R37" s="42"/>
+      <c r="S37" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T37" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="82.8">
+      <c r="T37" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="85.5">
       <c r="A38" s="28" t="s">
         <v>218</v>
       </c>
@@ -4764,34 +5154,34 @@
       <c r="J38" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="K38" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L38" s="46" t="s">
+      <c r="K38" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L38" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M38" s="46" t="s">
-        <v>466</v>
-      </c>
-      <c r="N38" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O38" s="46" t="s">
+      <c r="M38" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="N38" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O38" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P38" s="46" t="s">
+      <c r="P38" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q38" s="46"/>
-      <c r="R38" s="46"/>
-      <c r="S38" s="46" t="s">
+      <c r="Q38" s="42"/>
+      <c r="R38" s="42"/>
+      <c r="S38" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T38" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="82.8">
+      <c r="T38" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="85.5">
       <c r="A39" s="28" t="s">
         <v>221</v>
       </c>
@@ -4822,34 +5212,34 @@
       <c r="J39" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="K39" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L39" s="46" t="s">
+      <c r="K39" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L39" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M39" s="46" t="s">
-        <v>467</v>
-      </c>
-      <c r="N39" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O39" s="46" t="s">
+      <c r="M39" s="42" t="s">
+        <v>466</v>
+      </c>
+      <c r="N39" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O39" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P39" s="46" t="s">
+      <c r="P39" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="46"/>
-      <c r="S39" s="46" t="s">
+      <c r="Q39" s="42"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T39" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="82.8">
+      <c r="T39" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="85.5">
       <c r="A40" s="28" t="s">
         <v>223</v>
       </c>
@@ -4880,34 +5270,34 @@
       <c r="J40" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="K40" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L40" s="46" t="s">
+      <c r="K40" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L40" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M40" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="N40" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O40" s="46" t="s">
+      <c r="M40" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="N40" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O40" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="P40" s="46" t="s">
+      <c r="P40" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="Q40" s="46"/>
-      <c r="R40" s="46"/>
-      <c r="S40" s="46" t="s">
+      <c r="Q40" s="42"/>
+      <c r="R40" s="42"/>
+      <c r="S40" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="T40" s="46" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="69">
+      <c r="T40" s="42" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="71.25">
       <c r="A41" s="28" t="s">
         <v>226</v>
       </c>
@@ -4938,34 +5328,34 @@
       <c r="J41" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="K41" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L41" s="46" t="s">
+      <c r="K41" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L41" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M41" s="46" t="s">
+      <c r="M41" s="42" t="s">
+        <v>468</v>
+      </c>
+      <c r="N41" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O41" s="42" t="s">
         <v>469</v>
       </c>
-      <c r="N41" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O41" s="46" t="s">
+      <c r="P41" s="42" t="s">
         <v>470</v>
       </c>
-      <c r="P41" s="46" t="s">
+      <c r="Q41" s="42"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="T41" s="42" t="s">
         <v>471</v>
       </c>
-      <c r="Q41" s="46"/>
-      <c r="R41" s="46"/>
-      <c r="S41" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="T41" s="46" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" ht="41.4">
+    </row>
+    <row r="42" spans="1:20" ht="57">
       <c r="A42" s="28" t="s">
         <v>229</v>
       </c>
@@ -4996,28 +5386,34 @@
       <c r="J42" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="K42" s="46" t="s">
+      <c r="K42" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L42" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
-      <c r="O42" s="46"/>
-      <c r="P42" s="46"/>
-      <c r="Q42" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R42" s="46"/>
-      <c r="S42" s="46" t="s">
+      <c r="L42" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="N42" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O42" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="P42" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="42"/>
+      <c r="S42" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T42" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="41.4">
+      <c r="T42" s="42" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="57">
       <c r="A43" s="28" t="s">
         <v>239</v>
       </c>
@@ -5048,28 +5444,34 @@
       <c r="J43" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="K43" s="46" t="s">
+      <c r="K43" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L43" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="46"/>
-      <c r="P43" s="46"/>
-      <c r="Q43" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R43" s="46"/>
-      <c r="S43" s="46" t="s">
+      <c r="L43" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="N43" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O43" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="P43" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T43" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="41.4">
+      <c r="T43" s="42" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="57">
       <c r="A44" s="28" t="s">
         <v>242</v>
       </c>
@@ -5100,28 +5502,34 @@
       <c r="J44" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="K44" s="46" t="s">
+      <c r="K44" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L44" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
-      <c r="O44" s="46"/>
-      <c r="P44" s="46"/>
-      <c r="Q44" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R44" s="46"/>
-      <c r="S44" s="46" t="s">
+      <c r="L44" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="N44" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O44" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="P44" s="42" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T44" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="41.4">
+      <c r="T44" s="42" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="57">
       <c r="A45" s="28" t="s">
         <v>245</v>
       </c>
@@ -5152,28 +5560,34 @@
       <c r="J45" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="K45" s="46" t="s">
+      <c r="K45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L45" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="46"/>
-      <c r="P45" s="46"/>
-      <c r="Q45" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R45" s="46"/>
-      <c r="S45" s="46" t="s">
+      <c r="L45" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="42" t="s">
+        <v>494</v>
+      </c>
+      <c r="N45" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O45" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="P45" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T45" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" ht="41.4">
+      <c r="T45" s="42" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="114">
       <c r="A46" s="28" t="s">
         <v>248</v>
       </c>
@@ -5204,28 +5618,34 @@
       <c r="J46" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="K46" s="46" t="s">
+      <c r="K46" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L46" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
-      <c r="O46" s="46"/>
-      <c r="P46" s="46"/>
-      <c r="Q46" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R46" s="46"/>
-      <c r="S46" s="46" t="s">
+      <c r="L46" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="42" t="s">
+        <v>498</v>
+      </c>
+      <c r="N46" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O46" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="P46" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q46" s="42"/>
+      <c r="R46" s="42"/>
+      <c r="S46" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T46" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" ht="41.4">
+      <c r="T46" s="42" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="57">
       <c r="A47" s="28" t="s">
         <v>251</v>
       </c>
@@ -5256,28 +5676,34 @@
       <c r="J47" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="K47" s="46" t="s">
+      <c r="K47" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L47" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="46"/>
-      <c r="P47" s="46"/>
-      <c r="Q47" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R47" s="46"/>
-      <c r="S47" s="46" t="s">
+      <c r="L47" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="N47" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O47" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="P47" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q47" s="42"/>
+      <c r="R47" s="42"/>
+      <c r="S47" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T47" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="41.4">
+      <c r="T47" s="42" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="171">
       <c r="A48" s="28" t="s">
         <v>254</v>
       </c>
@@ -5308,28 +5734,36 @@
       <c r="J48" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="K48" s="46" t="s">
+      <c r="K48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L48" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="46"/>
-      <c r="Q48" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R48" s="46"/>
-      <c r="S48" s="46" t="s">
+      <c r="L48" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="N48" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O48" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="P48" s="42" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q48" s="42"/>
+      <c r="R48" s="42" t="s">
+        <v>505</v>
+      </c>
+      <c r="S48" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T48" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" ht="41.4">
+      <c r="T48" s="42" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="57">
       <c r="A49" s="28" t="s">
         <v>257</v>
       </c>
@@ -5360,28 +5794,34 @@
       <c r="J49" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="K49" s="46" t="s">
+      <c r="K49" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L49" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="46"/>
-      <c r="P49" s="46"/>
-      <c r="Q49" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R49" s="46"/>
-      <c r="S49" s="46" t="s">
+      <c r="L49" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="42" t="s">
+        <v>506</v>
+      </c>
+      <c r="N49" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O49" s="42" t="s">
+        <v>507</v>
+      </c>
+      <c r="P49" s="42" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q49" s="42"/>
+      <c r="R49" s="42"/>
+      <c r="S49" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T49" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" ht="41.4">
+      <c r="T49" s="42" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="185.25">
       <c r="A50" s="28" t="s">
         <v>260</v>
       </c>
@@ -5412,28 +5852,36 @@
       <c r="J50" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="K50" s="46" t="s">
+      <c r="K50" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L50" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R50" s="46"/>
-      <c r="S50" s="46" t="s">
+      <c r="L50" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M50" s="25" t="s">
+        <v>571</v>
+      </c>
+      <c r="N50" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O50" s="42" t="s">
+        <v>572</v>
+      </c>
+      <c r="P50" s="42" t="s">
+        <v>573</v>
+      </c>
+      <c r="Q50" s="42"/>
+      <c r="R50" s="42" t="s">
+        <v>505</v>
+      </c>
+      <c r="S50" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T50" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" ht="41.4">
+      <c r="T50" s="42" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="285">
       <c r="A51" s="28" t="s">
         <v>263</v>
       </c>
@@ -5464,28 +5912,38 @@
       <c r="J51" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="K51" s="46" t="s">
+      <c r="K51" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L51" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="R51" s="46"/>
-      <c r="S51" s="46" t="s">
+      <c r="L51" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M51" s="42" t="s">
+        <v>581</v>
+      </c>
+      <c r="N51" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O51" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="P51" s="42" t="s">
+        <v>583</v>
+      </c>
+      <c r="Q51" s="42" t="s">
+        <v>512</v>
+      </c>
+      <c r="R51" s="42" t="s">
+        <v>584</v>
+      </c>
+      <c r="S51" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T51" s="46" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" ht="41.4">
+      <c r="T51" s="42" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="42.75">
       <c r="A52" s="28" t="s">
         <v>266</v>
       </c>
@@ -5516,28 +5974,28 @@
       <c r="J52" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="K52" s="46" t="s">
+      <c r="K52" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L52" s="46" t="s">
+      <c r="L52" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R52" s="46"/>
-      <c r="S52" s="46" t="s">
+      <c r="M52" s="42"/>
+      <c r="N52" s="42"/>
+      <c r="O52" s="42"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R52" s="42"/>
+      <c r="S52" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T52" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" ht="41.4">
+      <c r="T52" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="42.75">
       <c r="A53" s="28" t="s">
         <v>274</v>
       </c>
@@ -5568,28 +6026,28 @@
       <c r="J53" s="29" t="s">
         <v>276</v>
       </c>
-      <c r="K53" s="46" t="s">
+      <c r="K53" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L53" s="46" t="s">
+      <c r="L53" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M53" s="46"/>
-      <c r="N53" s="46"/>
-      <c r="O53" s="46"/>
-      <c r="P53" s="46"/>
-      <c r="Q53" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R53" s="46"/>
-      <c r="S53" s="46" t="s">
+      <c r="M53" s="42"/>
+      <c r="N53" s="42"/>
+      <c r="O53" s="42"/>
+      <c r="P53" s="42"/>
+      <c r="Q53" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R53" s="42"/>
+      <c r="S53" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T53" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="41.4">
+      <c r="T53" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="42.75">
       <c r="A54" s="28" t="s">
         <v>277</v>
       </c>
@@ -5620,28 +6078,28 @@
       <c r="J54" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="46" t="s">
+      <c r="K54" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L54" s="46" t="s">
+      <c r="L54" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M54" s="46"/>
-      <c r="N54" s="46"/>
-      <c r="O54" s="46"/>
-      <c r="P54" s="46"/>
-      <c r="Q54" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R54" s="46"/>
-      <c r="S54" s="46" t="s">
+      <c r="M54" s="42"/>
+      <c r="N54" s="42"/>
+      <c r="O54" s="42"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R54" s="42"/>
+      <c r="S54" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T54" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" ht="41.4">
+      <c r="T54" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="42.75">
       <c r="A55" s="28" t="s">
         <v>280</v>
       </c>
@@ -5672,28 +6130,28 @@
       <c r="J55" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="K55" s="46" t="s">
+      <c r="K55" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L55" s="46" t="s">
+      <c r="L55" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M55" s="46"/>
-      <c r="N55" s="46"/>
-      <c r="O55" s="46"/>
-      <c r="P55" s="46"/>
-      <c r="Q55" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R55" s="46"/>
-      <c r="S55" s="46" t="s">
+      <c r="M55" s="42"/>
+      <c r="N55" s="42"/>
+      <c r="O55" s="42"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R55" s="42"/>
+      <c r="S55" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T55" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="41.4">
+      <c r="T55" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="42.75">
       <c r="A56" s="28" t="s">
         <v>283</v>
       </c>
@@ -5724,28 +6182,28 @@
       <c r="J56" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="K56" s="46" t="s">
+      <c r="K56" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L56" s="46" t="s">
+      <c r="L56" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M56" s="46"/>
-      <c r="N56" s="46"/>
-      <c r="O56" s="46"/>
-      <c r="P56" s="46"/>
-      <c r="Q56" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R56" s="46"/>
-      <c r="S56" s="46" t="s">
+      <c r="M56" s="42"/>
+      <c r="N56" s="42"/>
+      <c r="O56" s="42"/>
+      <c r="P56" s="42"/>
+      <c r="Q56" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R56" s="42"/>
+      <c r="S56" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T56" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" ht="41.4">
+      <c r="T56" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="42.75">
       <c r="A57" s="28" t="s">
         <v>286</v>
       </c>
@@ -5776,28 +6234,28 @@
       <c r="J57" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="K57" s="46" t="s">
+      <c r="K57" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L57" s="46" t="s">
+      <c r="L57" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M57" s="46"/>
-      <c r="N57" s="46"/>
-      <c r="O57" s="46"/>
-      <c r="P57" s="46"/>
-      <c r="Q57" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R57" s="46"/>
-      <c r="S57" s="46" t="s">
+      <c r="M57" s="42"/>
+      <c r="N57" s="42"/>
+      <c r="O57" s="42"/>
+      <c r="P57" s="42"/>
+      <c r="Q57" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R57" s="42"/>
+      <c r="S57" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T57" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="41.4">
+      <c r="T57" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="42.75">
       <c r="A58" s="28" t="s">
         <v>289</v>
       </c>
@@ -5828,28 +6286,28 @@
       <c r="J58" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="K58" s="46" t="s">
+      <c r="K58" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L58" s="46" t="s">
+      <c r="L58" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M58" s="46"/>
-      <c r="N58" s="46"/>
-      <c r="O58" s="46"/>
-      <c r="P58" s="46"/>
-      <c r="Q58" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R58" s="46"/>
-      <c r="S58" s="46" t="s">
+      <c r="M58" s="42"/>
+      <c r="N58" s="42"/>
+      <c r="O58" s="42"/>
+      <c r="P58" s="42"/>
+      <c r="Q58" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R58" s="42"/>
+      <c r="S58" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T58" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" ht="41.4">
+      <c r="T58" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="42.75">
       <c r="A59" s="28" t="s">
         <v>292</v>
       </c>
@@ -5880,28 +6338,28 @@
       <c r="J59" s="29" t="s">
         <v>294</v>
       </c>
-      <c r="K59" s="46" t="s">
+      <c r="K59" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L59" s="46" t="s">
+      <c r="L59" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M59" s="46"/>
-      <c r="N59" s="46"/>
-      <c r="O59" s="46"/>
-      <c r="P59" s="46"/>
-      <c r="Q59" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="R59" s="46"/>
-      <c r="S59" s="46" t="s">
+      <c r="M59" s="42"/>
+      <c r="N59" s="42"/>
+      <c r="O59" s="42"/>
+      <c r="P59" s="42"/>
+      <c r="Q59" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="R59" s="42"/>
+      <c r="S59" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T59" s="46" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" ht="41.4">
+      <c r="T59" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="42.75">
       <c r="A60" s="28" t="s">
         <v>295</v>
       </c>
@@ -5932,28 +6390,34 @@
       <c r="J60" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="K60" s="46" t="s">
+      <c r="K60" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L60" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M60" s="46"/>
-      <c r="N60" s="46"/>
-      <c r="O60" s="46"/>
-      <c r="P60" s="46"/>
-      <c r="Q60" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="R60" s="46"/>
-      <c r="S60" s="46" t="s">
+      <c r="L60" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M60" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="N60" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O60" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="P60" s="42" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q60" s="42"/>
+      <c r="R60" s="42"/>
+      <c r="S60" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T60" s="46" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" ht="41.4">
+      <c r="T60" s="42" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="57">
       <c r="A61" s="28" t="s">
         <v>303</v>
       </c>
@@ -5984,28 +6448,34 @@
       <c r="J61" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="K61" s="46" t="s">
+      <c r="K61" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L61" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M61" s="46"/>
-      <c r="N61" s="46"/>
-      <c r="O61" s="46"/>
-      <c r="P61" s="46"/>
-      <c r="Q61" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="R61" s="46"/>
-      <c r="S61" s="46" t="s">
+      <c r="L61" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M61" s="42" t="s">
+        <v>517</v>
+      </c>
+      <c r="N61" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O61" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="P61" s="42" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q61" s="42"/>
+      <c r="R61" s="42"/>
+      <c r="S61" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T61" s="46" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" ht="41.4">
+      <c r="T61" s="42" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="99.75">
       <c r="A62" s="28" t="s">
         <v>306</v>
       </c>
@@ -6036,28 +6506,34 @@
       <c r="J62" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="K62" s="46" t="s">
+      <c r="K62" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L62" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M62" s="46"/>
-      <c r="N62" s="46"/>
-      <c r="O62" s="46"/>
-      <c r="P62" s="46"/>
-      <c r="Q62" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="R62" s="46"/>
-      <c r="S62" s="46" t="s">
+      <c r="L62" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="42" t="s">
+        <v>519</v>
+      </c>
+      <c r="N62" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O62" s="42" t="s">
+        <v>520</v>
+      </c>
+      <c r="P62" s="42" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q62" s="42"/>
+      <c r="R62" s="42"/>
+      <c r="S62" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T62" s="46" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" ht="41.4">
+      <c r="T62" s="42" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="57">
       <c r="A63" s="28" t="s">
         <v>309</v>
       </c>
@@ -6088,28 +6564,34 @@
       <c r="J63" s="29" t="s">
         <v>311</v>
       </c>
-      <c r="K63" s="46" t="s">
+      <c r="K63" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L63" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M63" s="46"/>
-      <c r="N63" s="46"/>
-      <c r="O63" s="46"/>
-      <c r="P63" s="46"/>
-      <c r="Q63" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="R63" s="46"/>
-      <c r="S63" s="46" t="s">
+      <c r="L63" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M63" s="42" t="s">
+        <v>523</v>
+      </c>
+      <c r="N63" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O63" s="42" t="s">
+        <v>524</v>
+      </c>
+      <c r="P63" s="42" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q63" s="42"/>
+      <c r="R63" s="42"/>
+      <c r="S63" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T63" s="46" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" ht="41.4">
+      <c r="T63" s="42" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="42.75">
       <c r="A64" s="28" t="s">
         <v>312</v>
       </c>
@@ -6140,28 +6622,34 @@
       <c r="J64" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="K64" s="46" t="s">
+      <c r="K64" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L64" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M64" s="46"/>
-      <c r="N64" s="46"/>
-      <c r="O64" s="46"/>
-      <c r="P64" s="46"/>
-      <c r="Q64" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="R64" s="46"/>
-      <c r="S64" s="46" t="s">
+      <c r="L64" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M64" s="42" t="s">
+        <v>527</v>
+      </c>
+      <c r="N64" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O64" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="P64" s="42" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q64" s="42"/>
+      <c r="R64" s="42"/>
+      <c r="S64" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T64" s="46" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" ht="41.4">
+      <c r="T64" s="42" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="42.75">
       <c r="A65" s="28" t="s">
         <v>315</v>
       </c>
@@ -6192,28 +6680,34 @@
       <c r="J65" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="K65" s="46" t="s">
+      <c r="K65" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L65" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M65" s="46"/>
-      <c r="N65" s="46"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="46"/>
-      <c r="Q65" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="R65" s="46"/>
-      <c r="S65" s="46" t="s">
+      <c r="L65" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M65" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="N65" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O65" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="P65" s="42" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q65" s="42"/>
+      <c r="R65" s="42"/>
+      <c r="S65" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T65" s="46" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" ht="41.4">
+      <c r="T65" s="42" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="156.75">
       <c r="A66" s="28" t="s">
         <v>318</v>
       </c>
@@ -6244,28 +6738,34 @@
       <c r="J66" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="K66" s="46" t="s">
+      <c r="K66" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L66" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M66" s="46"/>
-      <c r="N66" s="46"/>
-      <c r="O66" s="46"/>
-      <c r="P66" s="46"/>
-      <c r="Q66" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="R66" s="46"/>
-      <c r="S66" s="46" t="s">
+      <c r="L66" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M66" s="42" t="s">
+        <v>533</v>
+      </c>
+      <c r="N66" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O66" s="42" t="s">
+        <v>534</v>
+      </c>
+      <c r="P66" s="42" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q66" s="42"/>
+      <c r="R66" s="42"/>
+      <c r="S66" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="T66" s="46" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" ht="55.2">
+      <c r="T66" s="42" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="256.5">
       <c r="A67" s="28" t="s">
         <v>321</v>
       </c>
@@ -6296,28 +6796,34 @@
       <c r="J67" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="K67" s="46" t="s">
+      <c r="K67" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L67" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M67" s="46"/>
-      <c r="N67" s="46"/>
-      <c r="O67" s="46"/>
-      <c r="P67" s="46"/>
-      <c r="Q67" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="R67" s="46"/>
-      <c r="S67" s="46" t="s">
+      <c r="L67" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M67" s="42" t="s">
+        <v>537</v>
+      </c>
+      <c r="N67" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O67" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="P67" s="42" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q67" s="42"/>
+      <c r="R67" s="42"/>
+      <c r="S67" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="T67" s="46" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" ht="55.2">
+      <c r="T67" s="42" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="409.5">
       <c r="A68" s="28" t="s">
         <v>331</v>
       </c>
@@ -6348,28 +6854,36 @@
       <c r="J68" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="K68" s="46" t="s">
+      <c r="K68" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L68" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M68" s="46"/>
-      <c r="N68" s="46"/>
-      <c r="O68" s="46"/>
-      <c r="P68" s="46"/>
-      <c r="Q68" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="R68" s="46"/>
-      <c r="S68" s="46" t="s">
+      <c r="L68" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M68" s="43" t="s">
+        <v>586</v>
+      </c>
+      <c r="N68" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O68" s="46" t="s">
+        <v>587</v>
+      </c>
+      <c r="P68" s="47" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q68" s="42" t="s">
+        <v>540</v>
+      </c>
+      <c r="R68" s="42"/>
+      <c r="S68" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="T68" s="46" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" ht="55.2">
+      <c r="T68" s="43" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="142.5">
       <c r="A69" s="28" t="s">
         <v>334</v>
       </c>
@@ -6400,28 +6914,36 @@
       <c r="J69" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="K69" s="46" t="s">
+      <c r="K69" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L69" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M69" s="46"/>
-      <c r="N69" s="46"/>
-      <c r="O69" s="46"/>
-      <c r="P69" s="46"/>
-      <c r="Q69" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="R69" s="46"/>
-      <c r="S69" s="46" t="s">
+      <c r="L69" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M69" s="42" t="s">
+        <v>592</v>
+      </c>
+      <c r="N69" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O69" s="42" t="s">
+        <v>594</v>
+      </c>
+      <c r="P69" s="42" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q69" s="42"/>
+      <c r="R69" s="46" t="s">
+        <v>593</v>
+      </c>
+      <c r="S69" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="T69" s="46" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" ht="55.2">
+      <c r="T69" s="42" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="99.75">
       <c r="A70" s="28" t="s">
         <v>337</v>
       </c>
@@ -6452,28 +6974,34 @@
       <c r="J70" s="29" t="s">
         <v>339</v>
       </c>
-      <c r="K70" s="46" t="s">
+      <c r="K70" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L70" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M70" s="46"/>
-      <c r="N70" s="46"/>
-      <c r="O70" s="46"/>
-      <c r="P70" s="46"/>
-      <c r="Q70" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="R70" s="46"/>
-      <c r="S70" s="46" t="s">
+      <c r="L70" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M70" s="42" t="s">
+        <v>541</v>
+      </c>
+      <c r="N70" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O70" s="42" t="s">
+        <v>542</v>
+      </c>
+      <c r="P70" s="42" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q70" s="42"/>
+      <c r="R70" s="42"/>
+      <c r="S70" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="T70" s="46" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" ht="55.2">
+      <c r="T70" s="42" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="128.25">
       <c r="A71" s="28" t="s">
         <v>340</v>
       </c>
@@ -6504,28 +7032,36 @@
       <c r="J71" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="K71" s="46" t="s">
+      <c r="K71" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L71" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="M71" s="46"/>
-      <c r="N71" s="46"/>
-      <c r="O71" s="46"/>
-      <c r="P71" s="46"/>
-      <c r="Q71" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="R71" s="46"/>
-      <c r="S71" s="46" t="s">
+      <c r="L71" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M71" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="N71" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O71" s="42" t="s">
+        <v>597</v>
+      </c>
+      <c r="P71" s="42" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q71" s="42" t="s">
+        <v>547</v>
+      </c>
+      <c r="R71" s="42"/>
+      <c r="S71" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="T71" s="46" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" ht="165.6">
+      <c r="T71" s="42" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="171">
       <c r="A72" s="28" t="s">
         <v>343</v>
       </c>
@@ -6556,34 +7092,34 @@
       <c r="J72" s="29" t="s">
         <v>349</v>
       </c>
-      <c r="K72" s="46" t="s">
+      <c r="K72" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L72" s="46" t="s">
+      <c r="L72" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="46" t="s">
-        <v>481</v>
-      </c>
-      <c r="N72" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O72" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="P72" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q72" s="46"/>
-      <c r="R72" s="46"/>
-      <c r="S72" s="46" t="s">
+      <c r="M72" s="42" t="s">
+        <v>474</v>
+      </c>
+      <c r="N72" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O72" s="42" t="s">
+        <v>475</v>
+      </c>
+      <c r="P72" s="42" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q72" s="42"/>
+      <c r="R72" s="42"/>
+      <c r="S72" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T72" s="46" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" ht="165.6">
+      <c r="T72" s="42" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="171">
       <c r="A73" s="28" t="s">
         <v>350</v>
       </c>
@@ -6614,34 +7150,34 @@
       <c r="J73" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="K73" s="46" t="s">
+      <c r="K73" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L73" s="46" t="s">
+      <c r="L73" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M73" s="46" t="s">
-        <v>485</v>
-      </c>
-      <c r="N73" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O73" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="P73" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q73" s="46"/>
-      <c r="R73" s="46"/>
-      <c r="S73" s="46" t="s">
+      <c r="M73" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="N73" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O73" s="42" t="s">
+        <v>475</v>
+      </c>
+      <c r="P73" s="42" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q73" s="42"/>
+      <c r="R73" s="42"/>
+      <c r="S73" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T73" s="46" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" ht="165.6">
+      <c r="T73" s="42" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="171">
       <c r="A74" s="28" t="s">
         <v>353</v>
       </c>
@@ -6672,34 +7208,34 @@
       <c r="J74" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="K74" s="46" t="s">
+      <c r="K74" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L74" s="46" t="s">
+      <c r="L74" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M74" s="46" t="s">
-        <v>486</v>
-      </c>
-      <c r="N74" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O74" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="P74" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q74" s="46"/>
-      <c r="R74" s="46"/>
-      <c r="S74" s="46" t="s">
+      <c r="M74" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="N74" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O74" s="42" t="s">
+        <v>475</v>
+      </c>
+      <c r="P74" s="42" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q74" s="42"/>
+      <c r="R74" s="42"/>
+      <c r="S74" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T74" s="46" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" ht="165.6">
+      <c r="T74" s="42" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="171">
       <c r="A75" s="28" t="s">
         <v>356</v>
       </c>
@@ -6730,34 +7266,34 @@
       <c r="J75" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="K75" s="46" t="s">
+      <c r="K75" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L75" s="46" t="s">
+      <c r="L75" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="M75" s="46" t="s">
-        <v>487</v>
-      </c>
-      <c r="N75" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O75" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="P75" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q75" s="46"/>
-      <c r="R75" s="46"/>
-      <c r="S75" s="46" t="s">
+      <c r="M75" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="N75" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O75" s="42" t="s">
+        <v>475</v>
+      </c>
+      <c r="P75" s="42" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q75" s="42"/>
+      <c r="R75" s="42"/>
+      <c r="S75" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T75" s="46" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" ht="82.8">
+      <c r="T75" s="42" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="57">
       <c r="A76" s="28" t="s">
         <v>359</v>
       </c>
@@ -6788,34 +7324,34 @@
       <c r="J76" s="29" t="s">
         <v>361</v>
       </c>
-      <c r="K76" s="46" t="s">
+      <c r="K76" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L76" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M76" s="46" t="s">
-        <v>488</v>
-      </c>
-      <c r="N76" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O76" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="P76" s="46" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q76" s="46"/>
-      <c r="R76" s="46"/>
-      <c r="S76" s="46" t="s">
+      <c r="L76" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M76" s="42" t="s">
+        <v>548</v>
+      </c>
+      <c r="N76" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O76" s="42" t="s">
+        <v>545</v>
+      </c>
+      <c r="P76" s="42" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q76" s="42"/>
+      <c r="R76" s="42"/>
+      <c r="S76" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="T76" s="46" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" ht="27.6">
+      <c r="T76" s="42" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="71.25">
       <c r="A77" s="28" t="s">
         <v>362</v>
       </c>
@@ -6846,24 +7382,34 @@
       <c r="J77" s="29" t="s">
         <v>369</v>
       </c>
-      <c r="K77" s="46" t="s">
+      <c r="K77" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L77" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M77" s="46"/>
-      <c r="N77" s="46"/>
-      <c r="O77" s="46"/>
-      <c r="P77" s="46"/>
-      <c r="Q77" s="46"/>
-      <c r="R77" s="46"/>
-      <c r="S77" s="46" t="s">
+      <c r="L77" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M77" s="42" t="s">
+        <v>550</v>
+      </c>
+      <c r="N77" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O77" s="42" t="s">
+        <v>551</v>
+      </c>
+      <c r="P77" s="42" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q77" s="42"/>
+      <c r="R77" s="42"/>
+      <c r="S77" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="T77" s="46"/>
-    </row>
-    <row r="78" spans="1:20" ht="27.6">
+      <c r="T77" s="42" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="42.75">
       <c r="A78" s="28" t="s">
         <v>370</v>
       </c>
@@ -6894,24 +7440,34 @@
       <c r="J78" s="29" t="s">
         <v>372</v>
       </c>
-      <c r="K78" s="46" t="s">
+      <c r="K78" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L78" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M78" s="46"/>
-      <c r="N78" s="46"/>
-      <c r="O78" s="46"/>
-      <c r="P78" s="46"/>
-      <c r="Q78" s="46"/>
-      <c r="R78" s="46"/>
-      <c r="S78" s="46" t="s">
+      <c r="L78" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M78" s="42" t="s">
+        <v>554</v>
+      </c>
+      <c r="N78" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O78" s="42" t="s">
+        <v>510</v>
+      </c>
+      <c r="P78" s="42" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q78" s="42"/>
+      <c r="R78" s="42"/>
+      <c r="S78" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="T78" s="46"/>
-    </row>
-    <row r="79" spans="1:20" ht="27.6">
+      <c r="T78" s="42" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="409.5">
       <c r="A79" s="28" t="s">
         <v>373</v>
       </c>
@@ -6942,24 +7498,34 @@
       <c r="J79" s="29" t="s">
         <v>375</v>
       </c>
-      <c r="K79" s="46" t="s">
+      <c r="K79" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L79" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M79" s="46"/>
-      <c r="N79" s="46"/>
-      <c r="O79" s="46"/>
-      <c r="P79" s="46"/>
-      <c r="Q79" s="46"/>
-      <c r="R79" s="46"/>
-      <c r="S79" s="46" t="s">
+      <c r="L79" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M79" s="42" t="s">
+        <v>556</v>
+      </c>
+      <c r="N79" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O79" s="42" t="s">
+        <v>557</v>
+      </c>
+      <c r="P79" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q79" s="42"/>
+      <c r="R79" s="42"/>
+      <c r="S79" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="T79" s="46"/>
-    </row>
-    <row r="80" spans="1:20" ht="27.6">
+      <c r="T79" s="42" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="85.5">
       <c r="A80" s="28" t="s">
         <v>376</v>
       </c>
@@ -6990,24 +7556,36 @@
       <c r="J80" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="K80" s="46" t="s">
+      <c r="K80" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L80" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M80" s="46"/>
-      <c r="N80" s="46"/>
-      <c r="O80" s="46"/>
-      <c r="P80" s="46"/>
-      <c r="Q80" s="46"/>
-      <c r="R80" s="46"/>
-      <c r="S80" s="46" t="s">
+      <c r="L80" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M80" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="N80" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O80" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="P80" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q80" s="42" t="s">
+        <v>560</v>
+      </c>
+      <c r="R80" s="42"/>
+      <c r="S80" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="T80" s="46"/>
-    </row>
-    <row r="81" spans="1:20" ht="27.6">
+      <c r="T80" s="42" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="85.5">
       <c r="A81" s="30" t="s">
         <v>379</v>
       </c>
@@ -7038,22 +7616,32 @@
       <c r="J81" s="31" t="s">
         <v>381</v>
       </c>
-      <c r="K81" s="46" t="s">
+      <c r="K81" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L81" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M81" s="46"/>
-      <c r="N81" s="46"/>
-      <c r="O81" s="46"/>
-      <c r="P81" s="46"/>
-      <c r="Q81" s="46"/>
-      <c r="R81" s="46"/>
-      <c r="S81" s="46" t="s">
+      <c r="L81" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="42" t="s">
+        <v>561</v>
+      </c>
+      <c r="N81" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O81" s="42" t="s">
+        <v>562</v>
+      </c>
+      <c r="P81" s="42" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q81" s="42"/>
+      <c r="R81" s="42"/>
+      <c r="S81" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="T81" s="46"/>
+      <c r="T81" s="42" t="s">
+        <v>564</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:L81">
@@ -7080,7 +7668,7 @@
     <dataValidation type="list" sqref="K2:K81" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Jerald,MD,Joyee,All Members,Shared"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L81" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" sqref="L2:L81" xr:uid="{DCF1EC1C-CC04-4C9A-8106-67F8E0406AD5}">
       <formula1>"Pass,Fail,Blocked,Retest,Not Run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7093,8 +7681,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -7106,19 +7694,19 @@
     <col min="8" max="8" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:8" ht="18">
+      <c r="A1" s="51" t="s">
         <v>382</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="32" t="s">
         <v>58</v>
       </c>
@@ -7144,7 +7732,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27.6">
+    <row r="4" spans="1:8" ht="28.5">
       <c r="A4" s="35"/>
       <c r="B4" s="36" t="s">
         <v>389</v>
@@ -7162,7 +7750,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27.6">
+    <row r="5" spans="1:8" ht="28.5">
       <c r="A5" s="35"/>
       <c r="B5" s="36" t="s">
         <v>392</v>
@@ -7180,7 +7768,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27.6">
+    <row r="6" spans="1:8" ht="28.5">
       <c r="A6" s="35"/>
       <c r="B6" s="36" t="s">
         <v>395</v>
@@ -7198,7 +7786,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27.6">
+    <row r="7" spans="1:8" ht="28.5">
       <c r="A7" s="35"/>
       <c r="B7" s="36" t="s">
         <v>397</v>
@@ -7216,7 +7804,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27.6">
+    <row r="8" spans="1:8" ht="28.5">
       <c r="A8" s="35"/>
       <c r="B8" s="36" t="s">
         <v>400</v>
@@ -7234,7 +7822,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27.6">
+    <row r="9" spans="1:8" ht="28.5">
       <c r="A9" s="38"/>
       <c r="B9" s="39" t="s">
         <v>403</v>
@@ -7250,6 +7838,110 @@
       <c r="G9" s="39"/>
       <c r="H9" s="40" t="s">
         <v>406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="114">
+      <c r="A10" t="s">
+        <v>566</v>
+      </c>
+      <c r="B10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>401</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>568</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>569</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="44">
+        <v>46285</v>
+      </c>
+      <c r="H10" s="43" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="85.5">
+      <c r="A11" t="s">
+        <v>572</v>
+      </c>
+      <c r="B11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>575</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>573</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="44">
+        <v>46285</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="156.75">
+      <c r="A12" t="s">
+        <v>577</v>
+      </c>
+      <c r="B12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C12" t="s">
+        <v>401</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>579</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>578</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="44">
+        <v>46285</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="285">
+      <c r="A13" t="s">
+        <v>587</v>
+      </c>
+      <c r="B13" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" t="s">
+        <v>401</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>590</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>589</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="44">
+        <v>46285</v>
+      </c>
+      <c r="H13" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>

--- a/docs/testing/sprint-2-test-cases.xlsx
+++ b/docs/testing/sprint-2-test-cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08_Personals\School Portfolio\GradNavi\docs\testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\COIT20273\GradNavi\docs\testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4227E4-B09E-4D5B-A830-BB415CE277D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F918C7B4-C200-4E90-A9C9-086BF21EC5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11820" yWindow="21480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="636">
   <si>
     <t>GradNavi Sprint 2 Test Dashboard</t>
   </si>
@@ -112,9 +110,6 @@
     <t>WBS 5.4 Career Recommendation API</t>
   </si>
   <si>
-    <t>Not present. careers/views.py is still the Django placeholder.</t>
-  </si>
-  <si>
     <t>Required</t>
   </si>
   <si>
@@ -1453,12 +1448,6 @@
     <t>S2-READ-12 validation completed with PASS.</t>
   </si>
   <si>
-    <t>WBS 5.7 exists on enamul/wbs-5.7-learning-roadmap-api but is not merged into feature/sprint-2.</t>
-  </si>
-  <si>
-    <t>Keep Blocked until MD's WBS 5.7 branch is rebased/merged into the shared Sprint 2 branch.</t>
-  </si>
-  <si>
     <t>Full backend regression suite passed registration, login, JWT and authentication-route tests with no Sprint 1 authentication regression.</t>
   </si>
   <si>
@@ -1850,6 +1839,110 @@
   </si>
   <si>
     <t>Chrome: Pass. Edge: Pass. Firefox: Pass.</t>
+  </si>
+  <si>
+    <t>API returned 200 OK with a scored Software Engineer 
+learning plan and 17 structured learning 
+suggestions for unresolved missing Skill gaps.</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified Learning Suggestions API returns structured suggestions for unresolved Skill gaps.</t>
+  </si>
+  <si>
+    <t>S2-EV-039</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-039-s2-learn-02-missing-skills-map-to-suggestions.png</t>
+  </si>
+  <si>
+    <t>17 missing Skill IDs exactly matched the 17 learning suggestion Skill IDs in the same order.</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified learning suggestions map exactly to unresolved missing Skills.</t>
+  </si>
+  <si>
+    <t>Below-requirement Skill 99 (Computers and Electronics) was returned as a learning suggestion with student score 50 below required level 89.00; exact Skill mapping verified.</t>
+  </si>
+  <si>
+    <t>S2-EV-040</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-040-s2-learn-03-below-requirement-suggestion.png</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified below-requirement Skill gaps are included in learning suggestions.</t>
+  </si>
+  <si>
+    <t>Skill 701 (Complex Problem Solving) met its required level (50/50.00) and was excluded from learning suggestions; no met Skills appeared in unresolved priorities.</t>
+  </si>
+  <si>
+    <t>S2-EV-041</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-041-s2-learn-04-met-skills-excluded.png</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified Skills meeting Career requirements are excluded from unresolved learning priorities.</t>
+  </si>
+  <si>
+    <t>Requested Career 39 (Software Engineer) was preserved in the learning plan and readiness result; all 17 suggestions belonged to the selected Career requirements.</t>
+  </si>
+  <si>
+    <t>S2-EV-042</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-042-s2-learn-05-selected-career-context.png</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified learning suggestions preserve the selected Career context and map only to its readiness requirements.</t>
+  </si>
+  <si>
+    <t>Empty Student Skill profile returned a controlled insufficient_profile result with no readiness score, Skill gaps, learning suggestions, or roadmap steps.</t>
+  </si>
+  <si>
+    <t>S2-EV-043</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-043-s2-learn-06-insufficient-profile-controlled.png</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified an empty Student Skill profile is handled as insufficient_profile without generating misleading suggestions.</t>
+  </si>
+  <si>
+    <t>Invalid career_id value "abc" returned 400 Bad Request with validation_error and field-level message "A valid integer is required."</t>
+  </si>
+  <si>
+    <t>S2-EV-044</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-044-s2-learn-07-invalid-request-validation.png</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified invalid learning requests are handled with a controlled API validation error.</t>
+  </si>
+  <si>
+    <t>Two executions with identical StudentProfile 2 and Career 39 input returned the same Career, scored status, readiness score (10.16), 17 suggestions, and identical structured suggestion results.</t>
+  </si>
+  <si>
+    <t>S2-EV-045</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-045-s2-learn-08-repeated-input-stable.png</t>
+  </si>
+  <si>
+    <t>WBS 5.7 is available on the shared branch. Verified repeated identical structured input produces stable deterministic learning suggestion results.</t>
+  </si>
+  <si>
+    <t>Implemented and available on the shared branch. Career Recommendation API testing completed.</t>
+  </si>
+  <si>
+    <t>Implemented and available on the shared branch. S2-LEARN-01 to S2-LEARN-08 completed successfully; all 8 tests passed.</t>
+  </si>
+  <si>
+    <t>S2-EV-038</t>
+  </si>
+  <si>
+    <t>docs/testing/evidence/sprint-2/S2-EV-038-s2-learn-01-structured-learning-suggestions.png</t>
   </si>
 </sst>
 </file>
@@ -1901,7 +1994,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1926,6 +2019,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2054,7 +2153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2195,6 +2294,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2213,6 +2327,33 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{03CE8168-D44C-42ED-BFF2-EB81F1D2AF07}"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2260,33 +2401,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2314,15 +2428,15 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Steps"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Expected Result"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Test Owner"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Status" dataDxfId="13" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Actual Result" dataDxfId="12" dataCellStyle="Normal 2"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tester" dataDxfId="11" dataCellStyle="Normal 2"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidence ID" dataDxfId="10" dataCellStyle="Normal 2"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidence Reference" dataDxfId="9" dataCellStyle="Normal 2"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Blocked Dependency" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Defect Reference" dataDxfId="7" dataCellStyle="Normal 2"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Automation" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Notes" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Status" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Actual Result" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tester" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidence ID" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidence Reference" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Blocked Dependency" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Defect Reference" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Automation" dataDxfId="1" dataCellStyle="Normal 2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Notes" dataDxfId="0" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2537,16 +2651,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.35" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7"/>
@@ -2611,7 +2725,7 @@
       </c>
       <c r="B5" s="10">
         <f>COUNTIF('Test Cases'!L2:L81,"Pass")</f>
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="11" t="s">
@@ -2661,7 +2775,7 @@
       </c>
       <c r="B7" s="10">
         <f>COUNTIF('Test Cases'!L2:L81,"Blocked")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="11" t="s">
@@ -2726,16 +2840,16 @@
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" ht="15.75">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" s="4" t="s">
@@ -2762,11 +2876,11 @@
       <c r="B13" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="52" t="s">
+        <v>632</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>25</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>26</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -2775,34 +2889,34 @@
     </row>
     <row r="14" spans="1:8" ht="28.5">
       <c r="A14" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>28</v>
-      </c>
       <c r="D14" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" ht="28.5">
+    <row r="15" spans="1:8" ht="42.75">
       <c r="A15" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>30</v>
+      <c r="C15" s="52" t="s">
+        <v>633</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -2811,16 +2925,16 @@
     </row>
     <row r="16" spans="1:8" ht="28.5">
       <c r="A16" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -2829,16 +2943,16 @@
     </row>
     <row r="17" spans="1:8" ht="28.5">
       <c r="A17" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>33</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>34</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -2856,23 +2970,23 @@
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="15">
-      <c r="A19" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
+      <c r="A19" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:8" ht="57">
       <c r="A20" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="25" t="s">
         <v>36</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>37</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -2883,10 +2997,10 @@
     </row>
     <row r="21" spans="1:8" ht="71.25">
       <c r="A21" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>38</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>39</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -2897,10 +3011,10 @@
     </row>
     <row r="22" spans="1:8" ht="57">
       <c r="A22" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="25" t="s">
         <v>40</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>41</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -2911,10 +3025,10 @@
     </row>
     <row r="23" spans="1:8" ht="85.5">
       <c r="A23" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="25" t="s">
         <v>42</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>43</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -2925,10 +3039,10 @@
     </row>
     <row r="24" spans="1:8" ht="71.25">
       <c r="A24" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>44</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>45</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -2975,96 +3089,96 @@
   <sheetData>
     <row r="1" spans="1:20" ht="28.9" customHeight="1">
       <c r="A1" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="D1" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="E1" s="27" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="H1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="I1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="J1" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="K1" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="L1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="M1" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="N1" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="41" t="s">
+      <c r="O1" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="41" t="s">
+      <c r="P1" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="41" t="s">
+      <c r="Q1" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="41" t="s">
+      <c r="R1" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="S1" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="T1" s="41" t="s">
         <v>62</v>
-      </c>
-      <c r="T1" s="41" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="57">
       <c r="A2" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="C2" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="D2" s="29" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>67</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="H2" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="I2" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="J2" s="29" t="s">
         <v>71</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>72</v>
       </c>
       <c r="K2" s="42" t="s">
         <v>7</v>
@@ -3073,56 +3187,56 @@
         <v>8</v>
       </c>
       <c r="M2" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="N2" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="N2" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O2" s="42" t="s">
+      <c r="P2" s="42" t="s">
         <v>408</v>
-      </c>
-      <c r="P2" s="42" t="s">
-        <v>409</v>
       </c>
       <c r="Q2" s="42"/>
       <c r="R2" s="42"/>
       <c r="S2" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T2" s="42" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="D3" s="29" t="s">
         <v>66</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>67</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="I3" s="29" t="s">
+      <c r="J3" s="29" t="s">
         <v>76</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>77</v>
       </c>
       <c r="K3" s="42" t="s">
         <v>7</v>
@@ -3131,56 +3245,56 @@
         <v>8</v>
       </c>
       <c r="M3" s="42" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N3" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O3" s="42" t="s">
+        <v>407</v>
+      </c>
+      <c r="P3" s="42" t="s">
         <v>408</v>
-      </c>
-      <c r="P3" s="42" t="s">
-        <v>409</v>
       </c>
       <c r="Q3" s="42"/>
       <c r="R3" s="42"/>
       <c r="S3" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T3" s="42" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="85.5">
       <c r="A4" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>66</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>67</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="I4" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>81</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>82</v>
       </c>
       <c r="K4" s="42" t="s">
         <v>7</v>
@@ -3189,56 +3303,56 @@
         <v>8</v>
       </c>
       <c r="M4" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="N4" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="N4" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O4" s="42" t="s">
+      <c r="P4" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P4" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q4" s="42"/>
       <c r="R4" s="42"/>
       <c r="S4" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T4" s="42" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="85.5">
       <c r="A5" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>85</v>
-      </c>
       <c r="D5" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="I5" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="J5" s="29" t="s">
         <v>88</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>89</v>
       </c>
       <c r="K5" s="42" t="s">
         <v>7</v>
@@ -3247,56 +3361,56 @@
         <v>8</v>
       </c>
       <c r="M5" s="42" t="s">
+        <v>416</v>
+      </c>
+      <c r="N5" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="42" t="s">
         <v>417</v>
       </c>
-      <c r="N5" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O5" s="42" t="s">
+      <c r="P5" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P5" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q5" s="42"/>
       <c r="R5" s="42"/>
       <c r="S5" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T5" s="42" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="85.5">
       <c r="A6" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="D6" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="I6" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="J6" s="29" t="s">
         <v>94</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>95</v>
       </c>
       <c r="K6" s="42" t="s">
         <v>7</v>
@@ -3305,56 +3419,56 @@
         <v>8</v>
       </c>
       <c r="M6" s="42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N6" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O6" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P6" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P6" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q6" s="42"/>
       <c r="R6" s="42"/>
       <c r="S6" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T6" s="42" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="85.5">
       <c r="A7" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="I7" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="J7" s="29" t="s">
         <v>99</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>100</v>
       </c>
       <c r="K7" s="42" t="s">
         <v>7</v>
@@ -3363,56 +3477,56 @@
         <v>8</v>
       </c>
       <c r="M7" s="42" t="s">
+        <v>422</v>
+      </c>
+      <c r="N7" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="42" t="s">
         <v>423</v>
       </c>
-      <c r="N7" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O7" s="42" t="s">
+      <c r="P7" s="42" t="s">
         <v>424</v>
-      </c>
-      <c r="P7" s="42" t="s">
-        <v>425</v>
       </c>
       <c r="Q7" s="42"/>
       <c r="R7" s="42"/>
       <c r="S7" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T7" s="42" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="85.5">
       <c r="A8" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="29" t="s">
+      <c r="D8" s="29" t="s">
         <v>102</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>103</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="I8" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="J8" s="29" t="s">
         <v>106</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>107</v>
       </c>
       <c r="K8" s="42" t="s">
         <v>18</v>
@@ -3421,56 +3535,56 @@
         <v>8</v>
       </c>
       <c r="M8" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="N8" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8" s="42" t="s">
         <v>427</v>
       </c>
-      <c r="N8" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O8" s="42" t="s">
+      <c r="P8" s="42" t="s">
         <v>428</v>
-      </c>
-      <c r="P8" s="42" t="s">
-        <v>429</v>
       </c>
       <c r="Q8" s="42"/>
       <c r="R8" s="42"/>
       <c r="S8" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T8" s="42" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="213.75">
       <c r="A9" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="29" t="s">
+      <c r="D9" s="29" t="s">
         <v>110</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>111</v>
       </c>
       <c r="E9" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="I9" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="J9" s="29" t="s">
         <v>114</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>115</v>
       </c>
       <c r="K9" s="42" t="s">
         <v>18</v>
@@ -3479,56 +3593,56 @@
         <v>8</v>
       </c>
       <c r="M9" s="42" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N9" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O9" s="42" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P9" s="42" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="Q9" s="42"/>
       <c r="R9" s="42"/>
       <c r="S9" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T9" s="42" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="85.5">
       <c r="A10" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="C10" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="D10" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E10" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="H10" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="I10" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="J10" s="29" t="s">
         <v>124</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>125</v>
       </c>
       <c r="K10" s="42" t="s">
         <v>7</v>
@@ -3537,56 +3651,56 @@
         <v>8</v>
       </c>
       <c r="M10" s="42" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N10" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P10" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P10" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q10" s="42"/>
       <c r="R10" s="42"/>
       <c r="S10" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T10" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="85.5">
       <c r="A11" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="D11" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G11" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" s="29" t="s">
         <v>127</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J11" s="29" t="s">
-        <v>128</v>
       </c>
       <c r="K11" s="42" t="s">
         <v>7</v>
@@ -3595,56 +3709,56 @@
         <v>8</v>
       </c>
       <c r="M11" s="42" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="N11" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O11" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P11" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P11" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q11" s="42"/>
       <c r="R11" s="42"/>
       <c r="S11" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T11" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="85.5">
       <c r="A12" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="D12" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E12" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G12" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="29" t="s">
         <v>130</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I12" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J12" s="29" t="s">
-        <v>131</v>
       </c>
       <c r="K12" s="42" t="s">
         <v>7</v>
@@ -3653,56 +3767,56 @@
         <v>8</v>
       </c>
       <c r="M12" s="42" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N12" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O12" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P12" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P12" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q12" s="42"/>
       <c r="R12" s="42"/>
       <c r="S12" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T12" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="85.5">
       <c r="A13" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="D13" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E13" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G13" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="29" t="s">
         <v>133</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J13" s="29" t="s">
-        <v>134</v>
       </c>
       <c r="K13" s="42" t="s">
         <v>7</v>
@@ -3711,56 +3825,56 @@
         <v>8</v>
       </c>
       <c r="M13" s="42" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N13" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O13" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P13" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P13" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q13" s="42"/>
       <c r="R13" s="42"/>
       <c r="S13" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T13" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="85.5">
       <c r="A14" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B14" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="D14" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E14" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="29" t="s">
         <v>136</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J14" s="29" t="s">
-        <v>137</v>
       </c>
       <c r="K14" s="42" t="s">
         <v>7</v>
@@ -3769,56 +3883,56 @@
         <v>8</v>
       </c>
       <c r="M14" s="42" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N14" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O14" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P14" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P14" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q14" s="42"/>
       <c r="R14" s="42"/>
       <c r="S14" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T14" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="85.5">
       <c r="A15" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B15" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="D15" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E15" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G15" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="29" t="s">
         <v>139</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J15" s="29" t="s">
-        <v>140</v>
       </c>
       <c r="K15" s="42" t="s">
         <v>7</v>
@@ -3827,56 +3941,56 @@
         <v>8</v>
       </c>
       <c r="M15" s="42" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N15" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O15" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P15" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P15" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q15" s="42"/>
       <c r="R15" s="42"/>
       <c r="S15" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T15" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="85.5">
       <c r="A16" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B16" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="D16" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E16" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G16" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="29" t="s">
         <v>142</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>143</v>
       </c>
       <c r="K16" s="42" t="s">
         <v>7</v>
@@ -3885,56 +3999,56 @@
         <v>8</v>
       </c>
       <c r="M16" s="42" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N16" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O16" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P16" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P16" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q16" s="42"/>
       <c r="R16" s="42"/>
       <c r="S16" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T16" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="85.5">
       <c r="A17" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B17" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="D17" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E17" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G17" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="29" t="s">
         <v>145</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I17" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J17" s="29" t="s">
-        <v>146</v>
       </c>
       <c r="K17" s="42" t="s">
         <v>7</v>
@@ -3943,56 +4057,56 @@
         <v>8</v>
       </c>
       <c r="M17" s="42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N17" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O17" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P17" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P17" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q17" s="42"/>
       <c r="R17" s="42"/>
       <c r="S17" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T17" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="85.5">
       <c r="A18" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B18" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E18" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G18" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="29" t="s">
         <v>148</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I18" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J18" s="29" t="s">
-        <v>149</v>
       </c>
       <c r="K18" s="42" t="s">
         <v>7</v>
@@ -4001,56 +4115,56 @@
         <v>8</v>
       </c>
       <c r="M18" s="42" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="N18" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O18" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P18" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P18" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q18" s="42"/>
       <c r="R18" s="42"/>
       <c r="S18" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T18" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="85.5">
       <c r="A19" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="D19" s="29" t="s">
         <v>119</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>120</v>
       </c>
       <c r="E19" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G19" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J19" s="29" t="s">
         <v>151</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="I19" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="J19" s="29" t="s">
-        <v>152</v>
       </c>
       <c r="K19" s="42" t="s">
         <v>7</v>
@@ -4059,56 +4173,56 @@
         <v>8</v>
       </c>
       <c r="M19" s="42" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N19" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O19" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="P19" s="42" t="s">
         <v>414</v>
-      </c>
-      <c r="P19" s="42" t="s">
-        <v>415</v>
       </c>
       <c r="Q19" s="42"/>
       <c r="R19" s="42"/>
       <c r="S19" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T19" s="42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="85.5">
       <c r="A20" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="C20" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="D20" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E20" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="H20" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="I20" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="J20" s="29" t="s">
         <v>160</v>
-      </c>
-      <c r="J20" s="29" t="s">
-        <v>161</v>
       </c>
       <c r="K20" s="42" t="s">
         <v>10</v>
@@ -4117,56 +4231,56 @@
         <v>8</v>
       </c>
       <c r="M20" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="N20" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O20" s="42" t="s">
         <v>442</v>
       </c>
-      <c r="N20" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O20" s="42" t="s">
+      <c r="P20" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P20" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q20" s="42"/>
       <c r="R20" s="42"/>
       <c r="S20" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T20" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="85.5">
       <c r="A21" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B21" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="D21" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E21" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G21" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J21" s="29" t="s">
         <v>163</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J21" s="29" t="s">
-        <v>164</v>
       </c>
       <c r="K21" s="42" t="s">
         <v>10</v>
@@ -4175,56 +4289,56 @@
         <v>8</v>
       </c>
       <c r="M21" s="42" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N21" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O21" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P21" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P21" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q21" s="42"/>
       <c r="R21" s="42"/>
       <c r="S21" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T21" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="85.5">
       <c r="A22" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="D22" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E22" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G22" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J22" s="29" t="s">
         <v>166</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J22" s="29" t="s">
-        <v>167</v>
       </c>
       <c r="K22" s="42" t="s">
         <v>10</v>
@@ -4233,56 +4347,56 @@
         <v>8</v>
       </c>
       <c r="M22" s="42" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N22" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O22" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P22" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P22" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q22" s="42"/>
       <c r="R22" s="42"/>
       <c r="S22" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T22" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="85.5">
       <c r="A23" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B23" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="D23" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E23" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G23" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" s="29" t="s">
         <v>169</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J23" s="29" t="s">
-        <v>170</v>
       </c>
       <c r="K23" s="42" t="s">
         <v>10</v>
@@ -4291,56 +4405,56 @@
         <v>8</v>
       </c>
       <c r="M23" s="42" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N23" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O23" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P23" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P23" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q23" s="42"/>
       <c r="R23" s="42"/>
       <c r="S23" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T23" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="85.5">
       <c r="A24" s="28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="D24" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D24" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E24" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G24" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J24" s="29" t="s">
         <v>172</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I24" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J24" s="29" t="s">
-        <v>173</v>
       </c>
       <c r="K24" s="42" t="s">
         <v>10</v>
@@ -4349,56 +4463,56 @@
         <v>8</v>
       </c>
       <c r="M24" s="42" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N24" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O24" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P24" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P24" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q24" s="42"/>
       <c r="R24" s="42"/>
       <c r="S24" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T24" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="85.5">
       <c r="A25" s="28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="D25" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E25" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G25" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="29" t="s">
         <v>175</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J25" s="29" t="s">
-        <v>176</v>
       </c>
       <c r="K25" s="42" t="s">
         <v>10</v>
@@ -4407,56 +4521,56 @@
         <v>8</v>
       </c>
       <c r="M25" s="42" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N25" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O25" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P25" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P25" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q25" s="42"/>
       <c r="R25" s="42"/>
       <c r="S25" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T25" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="85.5">
       <c r="A26" s="28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B26" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="D26" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E26" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H26" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="I26" s="29" t="s">
-        <v>160</v>
-      </c>
       <c r="J26" s="29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K26" s="42" t="s">
         <v>10</v>
@@ -4465,56 +4579,56 @@
         <v>8</v>
       </c>
       <c r="M26" s="42" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N26" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O26" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P26" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P26" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q26" s="42"/>
       <c r="R26" s="42"/>
       <c r="S26" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T26" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="85.5">
       <c r="A27" s="28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="D27" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E27" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G27" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="H27" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J27" s="29" t="s">
         <v>180</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I27" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J27" s="29" t="s">
-        <v>181</v>
       </c>
       <c r="K27" s="42" t="s">
         <v>10</v>
@@ -4523,56 +4637,56 @@
         <v>8</v>
       </c>
       <c r="M27" s="42" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N27" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O27" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P27" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P27" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q27" s="42"/>
       <c r="R27" s="42"/>
       <c r="S27" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T27" s="42" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="85.5">
       <c r="A28" s="28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B28" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="D28" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E28" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G28" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J28" s="29" t="s">
         <v>183</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I28" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J28" s="29" t="s">
-        <v>184</v>
       </c>
       <c r="K28" s="42" t="s">
         <v>10</v>
@@ -4581,56 +4695,56 @@
         <v>8</v>
       </c>
       <c r="M28" s="42" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N28" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O28" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P28" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P28" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q28" s="42"/>
       <c r="R28" s="42"/>
       <c r="S28" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T28" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="85.5">
       <c r="A29" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B29" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="D29" s="29" t="s">
         <v>155</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>156</v>
       </c>
       <c r="E29" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G29" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="J29" s="29" t="s">
         <v>186</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="I29" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="J29" s="29" t="s">
-        <v>187</v>
       </c>
       <c r="K29" s="42" t="s">
         <v>10</v>
@@ -4639,56 +4753,56 @@
         <v>8</v>
       </c>
       <c r="M29" s="42" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N29" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O29" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="P29" s="42" t="s">
         <v>443</v>
-      </c>
-      <c r="P29" s="42" t="s">
-        <v>444</v>
       </c>
       <c r="Q29" s="42"/>
       <c r="R29" s="42"/>
       <c r="S29" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T29" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="85.5">
       <c r="A30" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="C30" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="D30" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E30" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="G30" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="H30" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="H30" s="29" t="s">
+      <c r="I30" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="I30" s="29" t="s">
+      <c r="J30" s="29" t="s">
         <v>195</v>
-      </c>
-      <c r="J30" s="29" t="s">
-        <v>196</v>
       </c>
       <c r="K30" s="42" t="s">
         <v>7</v>
@@ -4697,56 +4811,56 @@
         <v>8</v>
       </c>
       <c r="M30" s="42" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N30" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O30" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P30" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P30" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q30" s="42"/>
       <c r="R30" s="42"/>
       <c r="S30" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T30" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="85.5">
       <c r="A31" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B31" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="D31" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E31" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G31" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J31" s="29" t="s">
         <v>198</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J31" s="29" t="s">
-        <v>199</v>
       </c>
       <c r="K31" s="42" t="s">
         <v>7</v>
@@ -4755,56 +4869,56 @@
         <v>8</v>
       </c>
       <c r="M31" s="42" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N31" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O31" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P31" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P31" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q31" s="42"/>
       <c r="R31" s="42"/>
       <c r="S31" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T31" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="85.5">
       <c r="A32" s="28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B32" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C32" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="D32" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E32" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G32" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J32" s="29" t="s">
         <v>201</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J32" s="29" t="s">
-        <v>202</v>
       </c>
       <c r="K32" s="42" t="s">
         <v>7</v>
@@ -4813,56 +4927,56 @@
         <v>8</v>
       </c>
       <c r="M32" s="42" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N32" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O32" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P32" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P32" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q32" s="42"/>
       <c r="R32" s="42"/>
       <c r="S32" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T32" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="85.5">
       <c r="A33" s="28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B33" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="D33" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E33" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G33" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J33" s="29" t="s">
         <v>204</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J33" s="29" t="s">
-        <v>205</v>
       </c>
       <c r="K33" s="42" t="s">
         <v>7</v>
@@ -4871,56 +4985,56 @@
         <v>8</v>
       </c>
       <c r="M33" s="42" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N33" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O33" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P33" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P33" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q33" s="42"/>
       <c r="R33" s="42"/>
       <c r="S33" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T33" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="85.5">
       <c r="A34" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B34" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="D34" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E34" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G34" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J34" s="29" t="s">
         <v>207</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I34" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J34" s="29" t="s">
-        <v>208</v>
       </c>
       <c r="K34" s="42" t="s">
         <v>7</v>
@@ -4929,56 +5043,56 @@
         <v>8</v>
       </c>
       <c r="M34" s="42" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N34" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O34" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P34" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P34" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q34" s="42"/>
       <c r="R34" s="42"/>
       <c r="S34" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T34" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="85.5">
       <c r="A35" s="28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B35" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C35" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="D35" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E35" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G35" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J35" s="29" t="s">
         <v>210</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J35" s="29" t="s">
-        <v>211</v>
       </c>
       <c r="K35" s="42" t="s">
         <v>7</v>
@@ -4987,56 +5101,56 @@
         <v>8</v>
       </c>
       <c r="M35" s="42" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N35" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O35" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P35" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P35" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q35" s="42"/>
       <c r="R35" s="42"/>
       <c r="S35" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T35" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="85.5">
       <c r="A36" s="28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B36" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C36" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="D36" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E36" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G36" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="H36" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I36" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J36" s="29" t="s">
         <v>213</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I36" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J36" s="29" t="s">
-        <v>214</v>
       </c>
       <c r="K36" s="42" t="s">
         <v>7</v>
@@ -5045,56 +5159,56 @@
         <v>8</v>
       </c>
       <c r="M36" s="42" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N36" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O36" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P36" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P36" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q36" s="42"/>
       <c r="R36" s="42"/>
       <c r="S36" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T36" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="85.5">
       <c r="A37" s="28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B37" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="D37" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E37" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G37" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I37" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J37" s="29" t="s">
         <v>216</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I37" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J37" s="29" t="s">
-        <v>217</v>
       </c>
       <c r="K37" s="42" t="s">
         <v>7</v>
@@ -5103,56 +5217,56 @@
         <v>8</v>
       </c>
       <c r="M37" s="42" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N37" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O37" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P37" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P37" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q37" s="42"/>
       <c r="R37" s="42"/>
       <c r="S37" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T37" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="85.5">
       <c r="A38" s="28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B38" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="D38" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E38" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G38" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="H38" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I38" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J38" s="29" t="s">
         <v>219</v>
-      </c>
-      <c r="H38" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I38" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J38" s="29" t="s">
-        <v>220</v>
       </c>
       <c r="K38" s="42" t="s">
         <v>7</v>
@@ -5161,56 +5275,56 @@
         <v>8</v>
       </c>
       <c r="M38" s="42" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N38" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O38" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P38" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P38" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q38" s="42"/>
       <c r="R38" s="42"/>
       <c r="S38" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T38" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="85.5">
       <c r="A39" s="28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B39" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="D39" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E39" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G39" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H39" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I39" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="I39" s="29" t="s">
-        <v>195</v>
-      </c>
       <c r="J39" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K39" s="42" t="s">
         <v>7</v>
@@ -5219,56 +5333,56 @@
         <v>8</v>
       </c>
       <c r="M39" s="42" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N39" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O39" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P39" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P39" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q39" s="42"/>
       <c r="R39" s="42"/>
       <c r="S39" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T39" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="85.5">
       <c r="A40" s="28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B40" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="D40" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E40" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G40" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="H40" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J40" s="29" t="s">
         <v>224</v>
-      </c>
-      <c r="H40" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I40" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J40" s="29" t="s">
-        <v>225</v>
       </c>
       <c r="K40" s="42" t="s">
         <v>7</v>
@@ -5277,56 +5391,56 @@
         <v>8</v>
       </c>
       <c r="M40" s="42" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N40" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O40" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="P40" s="42" t="s">
         <v>418</v>
-      </c>
-      <c r="P40" s="42" t="s">
-        <v>419</v>
       </c>
       <c r="Q40" s="42"/>
       <c r="R40" s="42"/>
       <c r="S40" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T40" s="42" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="71.25">
       <c r="A41" s="28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B41" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="D41" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>191</v>
       </c>
       <c r="E41" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G41" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="H41" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="J41" s="29" t="s">
         <v>227</v>
-      </c>
-      <c r="H41" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="I41" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="J41" s="29" t="s">
-        <v>228</v>
       </c>
       <c r="K41" s="42" t="s">
         <v>7</v>
@@ -5335,56 +5449,56 @@
         <v>8</v>
       </c>
       <c r="M41" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="N41" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O41" s="42" t="s">
         <v>468</v>
       </c>
-      <c r="N41" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O41" s="42" t="s">
+      <c r="P41" s="42" t="s">
         <v>469</v>
-      </c>
-      <c r="P41" s="42" t="s">
-        <v>470</v>
       </c>
       <c r="Q41" s="42"/>
       <c r="R41" s="42"/>
       <c r="S41" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T41" s="42" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="57">
       <c r="A42" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B42" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="C42" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="D42" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E42" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="G42" s="29" t="s">
+      <c r="H42" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="H42" s="29" t="s">
+      <c r="I42" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="I42" s="29" t="s">
+      <c r="J42" s="29" t="s">
         <v>236</v>
-      </c>
-      <c r="J42" s="29" t="s">
-        <v>237</v>
       </c>
       <c r="K42" s="42" t="s">
         <v>13</v>
@@ -5393,56 +5507,56 @@
         <v>8</v>
       </c>
       <c r="M42" s="42" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N42" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O42" s="42" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P42" s="42" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="Q42" s="42"/>
       <c r="R42" s="42"/>
       <c r="S42" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T42" s="42" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="57">
       <c r="A43" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B43" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="D43" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D43" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E43" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G43" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="H43" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I43" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J43" s="29" t="s">
         <v>240</v>
-      </c>
-      <c r="H43" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I43" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J43" s="29" t="s">
-        <v>241</v>
       </c>
       <c r="K43" s="42" t="s">
         <v>13</v>
@@ -5451,56 +5565,56 @@
         <v>8</v>
       </c>
       <c r="M43" s="42" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N43" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O43" s="42" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P43" s="42" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="Q43" s="42"/>
       <c r="R43" s="42"/>
       <c r="S43" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T43" s="42" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="57">
       <c r="A44" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B44" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="D44" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E44" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G44" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="H44" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I44" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J44" s="29" t="s">
         <v>243</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I44" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J44" s="29" t="s">
-        <v>244</v>
       </c>
       <c r="K44" s="42" t="s">
         <v>13</v>
@@ -5509,56 +5623,56 @@
         <v>8</v>
       </c>
       <c r="M44" s="42" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N44" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O44" s="42" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P44" s="42" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="Q44" s="42"/>
       <c r="R44" s="42"/>
       <c r="S44" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T44" s="42" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="57">
       <c r="A45" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B45" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C45" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="D45" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E45" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G45" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I45" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J45" s="29" t="s">
         <v>246</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I45" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J45" s="29" t="s">
-        <v>247</v>
       </c>
       <c r="K45" s="42" t="s">
         <v>13</v>
@@ -5567,56 +5681,56 @@
         <v>8</v>
       </c>
       <c r="M45" s="42" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="N45" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O45" s="42" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="P45" s="42" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="Q45" s="42"/>
       <c r="R45" s="42"/>
       <c r="S45" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T45" s="42" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="114">
       <c r="A46" s="28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B46" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="D46" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E46" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G46" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="H46" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I46" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J46" s="29" t="s">
         <v>249</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I46" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J46" s="29" t="s">
-        <v>250</v>
       </c>
       <c r="K46" s="42" t="s">
         <v>13</v>
@@ -5625,56 +5739,56 @@
         <v>8</v>
       </c>
       <c r="M46" s="42" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="N46" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O46" s="42" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="P46" s="42" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="Q46" s="42"/>
       <c r="R46" s="42"/>
       <c r="S46" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T46" s="42" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="57">
       <c r="A47" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B47" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C47" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="D47" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E47" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G47" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I47" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J47" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="H47" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I47" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J47" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="K47" s="42" t="s">
         <v>13</v>
@@ -5683,56 +5797,56 @@
         <v>8</v>
       </c>
       <c r="M47" s="42" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="N47" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O47" s="42" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="P47" s="42" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="Q47" s="42"/>
       <c r="R47" s="42"/>
       <c r="S47" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T47" s="42" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="171">
       <c r="A48" s="28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B48" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="D48" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E48" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G48" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="H48" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I48" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J48" s="29" t="s">
         <v>255</v>
-      </c>
-      <c r="H48" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I48" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J48" s="29" t="s">
-        <v>256</v>
       </c>
       <c r="K48" s="42" t="s">
         <v>13</v>
@@ -5741,58 +5855,58 @@
         <v>8</v>
       </c>
       <c r="M48" s="25" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="N48" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O48" s="42" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="P48" s="42" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="Q48" s="42"/>
       <c r="R48" s="42" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="S48" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T48" s="42" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="57">
       <c r="A49" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B49" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="D49" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E49" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G49" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="H49" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I49" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J49" s="29" t="s">
         <v>258</v>
-      </c>
-      <c r="H49" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I49" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J49" s="29" t="s">
-        <v>259</v>
       </c>
       <c r="K49" s="42" t="s">
         <v>13</v>
@@ -5801,56 +5915,56 @@
         <v>8</v>
       </c>
       <c r="M49" s="42" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="N49" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O49" s="42" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="P49" s="42" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="Q49" s="42"/>
       <c r="R49" s="42"/>
       <c r="S49" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T49" s="42" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="185.25">
       <c r="A50" s="28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B50" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C50" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="D50" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E50" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G50" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="H50" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I50" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J50" s="29" t="s">
         <v>261</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I50" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J50" s="29" t="s">
-        <v>262</v>
       </c>
       <c r="K50" s="42" t="s">
         <v>13</v>
@@ -5859,58 +5973,58 @@
         <v>8</v>
       </c>
       <c r="M50" s="25" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="N50" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O50" s="42" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="P50" s="42" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="Q50" s="42"/>
       <c r="R50" s="42" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="S50" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T50" s="42" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="285">
       <c r="A51" s="28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B51" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C51" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="D51" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>232</v>
       </c>
       <c r="E51" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G51" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="H51" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I51" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="J51" s="29" t="s">
         <v>264</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="I51" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="J51" s="29" t="s">
-        <v>265</v>
       </c>
       <c r="K51" s="42" t="s">
         <v>13</v>
@@ -5919,476 +6033,524 @@
         <v>8</v>
       </c>
       <c r="M51" s="42" t="s">
+        <v>578</v>
+      </c>
+      <c r="N51" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O51" s="46" t="s">
+        <v>579</v>
+      </c>
+      <c r="P51" s="42" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q51" s="42" t="s">
+        <v>509</v>
+      </c>
+      <c r="R51" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="N51" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O51" s="46" t="s">
+      <c r="S51" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="T51" s="42" t="s">
         <v>582</v>
       </c>
-      <c r="P51" s="42" t="s">
-        <v>583</v>
-      </c>
-      <c r="Q51" s="42" t="s">
-        <v>512</v>
-      </c>
-      <c r="R51" s="42" t="s">
-        <v>584</v>
-      </c>
-      <c r="S51" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="T51" s="42" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" ht="42.75">
+    </row>
+    <row r="52" spans="1:20" ht="71.25">
       <c r="A52" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="B52" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="C52" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C52" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D52" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E52" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F52" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="G52" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="G52" s="29" t="s">
+      <c r="H52" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="H52" s="29" t="s">
+      <c r="I52" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="I52" s="29" t="s">
+      <c r="J52" s="29" t="s">
         <v>272</v>
-      </c>
-      <c r="J52" s="29" t="s">
-        <v>273</v>
       </c>
       <c r="K52" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L52" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M52" s="42"/>
-      <c r="N52" s="42"/>
-      <c r="O52" s="42"/>
-      <c r="P52" s="42"/>
-      <c r="Q52" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M52" s="51" t="s">
+        <v>602</v>
+      </c>
+      <c r="N52" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="O52" s="48" t="s">
+        <v>634</v>
+      </c>
+      <c r="P52" s="51" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q52" s="42"/>
       <c r="R52" s="42"/>
       <c r="S52" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="T52" s="42" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" ht="42.75">
+        <v>107</v>
+      </c>
+      <c r="T52" s="51" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="57">
       <c r="A53" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B53" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C53" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C53" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D53" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E53" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G53" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I53" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J53" s="29" t="s">
         <v>275</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="I53" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="J53" s="29" t="s">
-        <v>276</v>
       </c>
       <c r="K53" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L53" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M53" s="42"/>
-      <c r="N53" s="42"/>
-      <c r="O53" s="42"/>
-      <c r="P53" s="42"/>
-      <c r="Q53" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M53" s="42" t="s">
+        <v>606</v>
+      </c>
+      <c r="N53" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="O53" s="48" t="s">
+        <v>604</v>
+      </c>
+      <c r="P53" s="50" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q53" s="42"/>
       <c r="R53" s="42"/>
       <c r="S53" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T53" s="42" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="42.75">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="57">
       <c r="A54" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B54" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C54" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D54" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E54" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G54" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="H54" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I54" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J54" s="29" t="s">
         <v>278</v>
-      </c>
-      <c r="H54" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="I54" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="J54" s="29" t="s">
-        <v>279</v>
       </c>
       <c r="K54" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L54" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M54" s="42"/>
-      <c r="N54" s="42"/>
-      <c r="O54" s="42"/>
-      <c r="P54" s="42"/>
-      <c r="Q54" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M54" s="42" t="s">
+        <v>608</v>
+      </c>
+      <c r="N54" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="O54" s="42" t="s">
+        <v>609</v>
+      </c>
+      <c r="P54" s="50" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q54" s="42"/>
       <c r="R54" s="42"/>
       <c r="S54" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T54" s="42" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" ht="42.75">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="57">
       <c r="A55" s="28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B55" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C55" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C55" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D55" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E55" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G55" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="H55" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I55" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J55" s="29" t="s">
         <v>281</v>
-      </c>
-      <c r="H55" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="I55" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="J55" s="29" t="s">
-        <v>282</v>
       </c>
       <c r="K55" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L55" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M55" s="42"/>
-      <c r="N55" s="42"/>
-      <c r="O55" s="42"/>
-      <c r="P55" s="42"/>
-      <c r="Q55" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M55" s="42" t="s">
+        <v>612</v>
+      </c>
+      <c r="N55" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="O55" s="42" t="s">
+        <v>613</v>
+      </c>
+      <c r="P55" s="42" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q55" s="42"/>
       <c r="R55" s="42"/>
       <c r="S55" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T55" s="42" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="42.75">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="71.25">
       <c r="A56" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B56" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C56" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C56" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D56" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E56" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G56" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="H56" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J56" s="29" t="s">
         <v>284</v>
-      </c>
-      <c r="H56" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="I56" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="J56" s="29" t="s">
-        <v>285</v>
       </c>
       <c r="K56" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L56" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M56" s="42"/>
-      <c r="N56" s="42"/>
-      <c r="O56" s="42"/>
-      <c r="P56" s="42"/>
-      <c r="Q56" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M56" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="N56" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="O56" s="42" t="s">
+        <v>617</v>
+      </c>
+      <c r="P56" s="42" t="s">
+        <v>618</v>
+      </c>
+      <c r="Q56" s="42"/>
       <c r="R56" s="42"/>
       <c r="S56" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T56" s="42" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" ht="42.75">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="71.25">
       <c r="A57" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B57" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C57" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C57" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D57" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E57" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G57" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="H57" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I57" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J57" s="29" t="s">
         <v>287</v>
-      </c>
-      <c r="H57" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="I57" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="J57" s="29" t="s">
-        <v>288</v>
       </c>
       <c r="K57" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L57" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M57" s="42"/>
-      <c r="N57" s="42"/>
-      <c r="O57" s="42"/>
-      <c r="P57" s="42"/>
-      <c r="Q57" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M57" s="42" t="s">
+        <v>620</v>
+      </c>
+      <c r="N57" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="O57" s="42" t="s">
+        <v>621</v>
+      </c>
+      <c r="P57" s="42" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q57" s="42"/>
       <c r="R57" s="42"/>
       <c r="S57" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T57" s="42" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="42.75">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="57">
       <c r="A58" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B58" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C58" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C58" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D58" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E58" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G58" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="H58" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I58" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J58" s="29" t="s">
         <v>290</v>
-      </c>
-      <c r="H58" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="I58" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="J58" s="29" t="s">
-        <v>291</v>
       </c>
       <c r="K58" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L58" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M58" s="42"/>
-      <c r="N58" s="42"/>
-      <c r="O58" s="42"/>
-      <c r="P58" s="42"/>
-      <c r="Q58" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M58" s="42" t="s">
+        <v>624</v>
+      </c>
+      <c r="N58" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="O58" s="42" t="s">
+        <v>625</v>
+      </c>
+      <c r="P58" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q58" s="42"/>
       <c r="R58" s="42"/>
       <c r="S58" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T58" s="42" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" ht="42.75">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="71.25">
       <c r="A59" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B59" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C59" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C59" s="29" t="s">
-        <v>268</v>
-      </c>
       <c r="D59" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E59" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G59" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="H59" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I59" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J59" s="29" t="s">
         <v>293</v>
-      </c>
-      <c r="H59" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="I59" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="J59" s="29" t="s">
-        <v>294</v>
       </c>
       <c r="K59" s="42" t="s">
         <v>10</v>
       </c>
       <c r="L59" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="M59" s="42"/>
-      <c r="N59" s="42"/>
-      <c r="O59" s="42"/>
-      <c r="P59" s="42"/>
-      <c r="Q59" s="42" t="s">
-        <v>472</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M59" s="42" t="s">
+        <v>628</v>
+      </c>
+      <c r="N59" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="O59" s="42" t="s">
+        <v>629</v>
+      </c>
+      <c r="P59" s="42" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q59" s="42"/>
       <c r="R59" s="42"/>
       <c r="S59" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T59" s="42" t="s">
-        <v>473</v>
+        <v>631</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="42.75">
       <c r="A60" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B60" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="B60" s="29" t="s">
+      <c r="C60" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C60" s="29" t="s">
-        <v>297</v>
-      </c>
       <c r="D60" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E60" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F60" s="29" t="s">
+        <v>297</v>
+      </c>
+      <c r="G60" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="G60" s="29" t="s">
+      <c r="H60" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="H60" s="29" t="s">
+      <c r="I60" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="I60" s="29" t="s">
+      <c r="J60" s="29" t="s">
         <v>301</v>
-      </c>
-      <c r="J60" s="29" t="s">
-        <v>302</v>
       </c>
       <c r="K60" s="42" t="s">
         <v>13</v>
@@ -6397,56 +6559,56 @@
         <v>8</v>
       </c>
       <c r="M60" s="42" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="N60" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O60" s="42" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="P60" s="42" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="Q60" s="42"/>
       <c r="R60" s="42"/>
       <c r="S60" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T60" s="42" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="57">
       <c r="A61" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B61" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C61" s="29" t="s">
-        <v>297</v>
-      </c>
       <c r="D61" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G61" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="I61" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="J61" s="29" t="s">
         <v>304</v>
-      </c>
-      <c r="H61" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="I61" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="J61" s="29" t="s">
-        <v>305</v>
       </c>
       <c r="K61" s="42" t="s">
         <v>13</v>
@@ -6455,56 +6617,56 @@
         <v>8</v>
       </c>
       <c r="M61" s="42" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="N61" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O61" s="42" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="P61" s="42" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="Q61" s="42"/>
       <c r="R61" s="42"/>
       <c r="S61" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T61" s="42" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="99.75">
       <c r="A62" s="28" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B62" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C62" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C62" s="29" t="s">
-        <v>297</v>
-      </c>
       <c r="D62" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E62" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G62" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="H62" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="I62" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="J62" s="29" t="s">
         <v>307</v>
-      </c>
-      <c r="H62" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="I62" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="J62" s="29" t="s">
-        <v>308</v>
       </c>
       <c r="K62" s="42" t="s">
         <v>13</v>
@@ -6513,56 +6675,56 @@
         <v>8</v>
       </c>
       <c r="M62" s="42" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="N62" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O62" s="42" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="P62" s="42" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="Q62" s="42"/>
       <c r="R62" s="42"/>
       <c r="S62" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T62" s="42" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="57">
       <c r="A63" s="28" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B63" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C63" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C63" s="29" t="s">
-        <v>297</v>
-      </c>
       <c r="D63" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E63" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F63" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G63" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="H63" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="I63" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="J63" s="29" t="s">
         <v>310</v>
-      </c>
-      <c r="H63" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="I63" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="J63" s="29" t="s">
-        <v>311</v>
       </c>
       <c r="K63" s="42" t="s">
         <v>13</v>
@@ -6571,56 +6733,56 @@
         <v>8</v>
       </c>
       <c r="M63" s="42" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N63" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O63" s="42" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="P63" s="42" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="Q63" s="42"/>
       <c r="R63" s="42"/>
       <c r="S63" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T63" s="42" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="64" spans="1:20" ht="42.75">
       <c r="A64" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B64" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C64" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C64" s="29" t="s">
-        <v>297</v>
-      </c>
       <c r="D64" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E64" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G64" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="H64" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="I64" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="J64" s="29" t="s">
         <v>313</v>
-      </c>
-      <c r="H64" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="I64" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="J64" s="29" t="s">
-        <v>314</v>
       </c>
       <c r="K64" s="42" t="s">
         <v>13</v>
@@ -6629,56 +6791,56 @@
         <v>8</v>
       </c>
       <c r="M64" s="42" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="N64" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O64" s="42" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="P64" s="42" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="Q64" s="42"/>
       <c r="R64" s="42"/>
       <c r="S64" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T64" s="42" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="65" spans="1:20" ht="42.75">
       <c r="A65" s="28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B65" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C65" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C65" s="29" t="s">
-        <v>297</v>
-      </c>
       <c r="D65" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E65" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F65" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G65" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="H65" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="I65" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="J65" s="29" t="s">
         <v>316</v>
-      </c>
-      <c r="H65" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="I65" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="J65" s="29" t="s">
-        <v>317</v>
       </c>
       <c r="K65" s="42" t="s">
         <v>13</v>
@@ -6687,56 +6849,56 @@
         <v>8</v>
       </c>
       <c r="M65" s="42" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="N65" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O65" s="42" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="P65" s="42" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="Q65" s="42"/>
       <c r="R65" s="42"/>
       <c r="S65" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T65" s="42" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="66" spans="1:20" ht="156.75">
       <c r="A66" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B66" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C66" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C66" s="29" t="s">
-        <v>297</v>
-      </c>
       <c r="D66" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E66" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G66" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="H66" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="I66" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="J66" s="29" t="s">
         <v>319</v>
-      </c>
-      <c r="H66" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="I66" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="J66" s="29" t="s">
-        <v>320</v>
       </c>
       <c r="K66" s="42" t="s">
         <v>16</v>
@@ -6745,56 +6907,56 @@
         <v>8</v>
       </c>
       <c r="M66" s="42" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="N66" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O66" s="42" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="P66" s="42" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="Q66" s="42"/>
       <c r="R66" s="42"/>
       <c r="S66" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T66" s="42" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="67" spans="1:20" ht="256.5">
       <c r="A67" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="B67" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="B67" s="29" t="s">
+      <c r="C67" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="D67" s="29" t="s">
         <v>323</v>
-      </c>
-      <c r="D67" s="29" t="s">
-        <v>324</v>
       </c>
       <c r="E67" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F67" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="G67" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="G67" s="29" t="s">
+      <c r="H67" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="H67" s="29" t="s">
+      <c r="I67" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="I67" s="29" t="s">
+      <c r="J67" s="29" t="s">
         <v>328</v>
-      </c>
-      <c r="J67" s="29" t="s">
-        <v>329</v>
       </c>
       <c r="K67" s="42" t="s">
         <v>16</v>
@@ -6803,56 +6965,56 @@
         <v>8</v>
       </c>
       <c r="M67" s="42" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="N67" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O67" s="42" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P67" s="42" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="Q67" s="42"/>
       <c r="R67" s="42"/>
       <c r="S67" s="42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T67" s="42" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="409.5">
       <c r="A68" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B68" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="C68" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="D68" s="29" t="s">
         <v>323</v>
-      </c>
-      <c r="D68" s="29" t="s">
-        <v>324</v>
       </c>
       <c r="E68" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G68" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="H68" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="I68" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="J68" s="29" t="s">
         <v>332</v>
-      </c>
-      <c r="H68" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="I68" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="J68" s="29" t="s">
-        <v>333</v>
       </c>
       <c r="K68" s="42" t="s">
         <v>16</v>
@@ -6861,58 +7023,58 @@
         <v>8</v>
       </c>
       <c r="M68" s="43" t="s">
+        <v>583</v>
+      </c>
+      <c r="N68" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O68" s="46" t="s">
+        <v>584</v>
+      </c>
+      <c r="P68" s="47" t="s">
         <v>586</v>
       </c>
-      <c r="N68" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O68" s="46" t="s">
-        <v>587</v>
-      </c>
-      <c r="P68" s="47" t="s">
-        <v>589</v>
-      </c>
       <c r="Q68" s="42" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="R68" s="42"/>
       <c r="S68" s="42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T68" s="43" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="142.5">
       <c r="A69" s="28" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B69" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="C69" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="D69" s="29" t="s">
         <v>323</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>324</v>
       </c>
       <c r="E69" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G69" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="H69" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="I69" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="J69" s="29" t="s">
         <v>335</v>
-      </c>
-      <c r="H69" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="I69" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="J69" s="29" t="s">
-        <v>336</v>
       </c>
       <c r="K69" s="42" t="s">
         <v>16</v>
@@ -6921,58 +7083,58 @@
         <v>8</v>
       </c>
       <c r="M69" s="42" t="s">
+        <v>589</v>
+      </c>
+      <c r="N69" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O69" s="42" t="s">
+        <v>591</v>
+      </c>
+      <c r="P69" s="42" t="s">
         <v>592</v>
-      </c>
-      <c r="N69" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O69" s="42" t="s">
-        <v>594</v>
-      </c>
-      <c r="P69" s="42" t="s">
-        <v>595</v>
       </c>
       <c r="Q69" s="42"/>
       <c r="R69" s="46" t="s">
+        <v>590</v>
+      </c>
+      <c r="S69" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="T69" s="42" t="s">
         <v>593</v>
-      </c>
-      <c r="S69" s="42" t="s">
-        <v>330</v>
-      </c>
-      <c r="T69" s="42" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="99.75">
       <c r="A70" s="28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B70" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="C70" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="D70" s="29" t="s">
         <v>323</v>
-      </c>
-      <c r="D70" s="29" t="s">
-        <v>324</v>
       </c>
       <c r="E70" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F70" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G70" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="H70" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="I70" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="J70" s="29" t="s">
         <v>338</v>
-      </c>
-      <c r="H70" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="I70" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="J70" s="29" t="s">
-        <v>339</v>
       </c>
       <c r="K70" s="42" t="s">
         <v>16</v>
@@ -6981,56 +7143,56 @@
         <v>8</v>
       </c>
       <c r="M70" s="42" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N70" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O70" s="42" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="P70" s="42" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="Q70" s="42"/>
       <c r="R70" s="42"/>
       <c r="S70" s="42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T70" s="42" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="128.25">
       <c r="A71" s="28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B71" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="C71" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="D71" s="29" t="s">
         <v>323</v>
-      </c>
-      <c r="D71" s="29" t="s">
-        <v>324</v>
       </c>
       <c r="E71" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F71" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G71" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="H71" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="I71" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="J71" s="29" t="s">
         <v>341</v>
-      </c>
-      <c r="H71" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="I71" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="J71" s="29" t="s">
-        <v>342</v>
       </c>
       <c r="K71" s="42" t="s">
         <v>16</v>
@@ -7039,58 +7201,58 @@
         <v>8</v>
       </c>
       <c r="M71" s="42" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="N71" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O71" s="42" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="P71" s="42" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="Q71" s="42" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R71" s="42"/>
       <c r="S71" s="42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T71" s="42" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="72" spans="1:20" ht="171">
       <c r="A72" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="B72" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="B72" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="C72" s="29" t="s">
-        <v>344</v>
-      </c>
       <c r="D72" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E72" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F72" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="G72" s="29" t="s">
         <v>345</v>
       </c>
-      <c r="G72" s="29" t="s">
+      <c r="H72" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="H72" s="29" t="s">
+      <c r="I72" s="29" t="s">
         <v>347</v>
       </c>
-      <c r="I72" s="29" t="s">
+      <c r="J72" s="29" t="s">
         <v>348</v>
-      </c>
-      <c r="J72" s="29" t="s">
-        <v>349</v>
       </c>
       <c r="K72" s="42" t="s">
         <v>16</v>
@@ -7099,56 +7261,56 @@
         <v>8</v>
       </c>
       <c r="M72" s="42" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N72" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O72" s="42" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="P72" s="42" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Q72" s="42"/>
       <c r="R72" s="42"/>
       <c r="S72" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T72" s="42" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="73" spans="1:20" ht="171">
       <c r="A73" s="28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E73" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F73" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G73" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="H73" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="I73" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="J73" s="29" t="s">
         <v>351</v>
-      </c>
-      <c r="H73" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="I73" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="J73" s="29" t="s">
-        <v>352</v>
       </c>
       <c r="K73" s="42" t="s">
         <v>16</v>
@@ -7157,56 +7319,56 @@
         <v>8</v>
       </c>
       <c r="M73" s="42" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="N73" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O73" s="42" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="P73" s="42" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Q73" s="42"/>
       <c r="R73" s="42"/>
       <c r="S73" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T73" s="42" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="74" spans="1:20" ht="171">
       <c r="A74" s="28" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E74" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G74" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="H74" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="I74" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="J74" s="29" t="s">
         <v>354</v>
-      </c>
-      <c r="H74" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="I74" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="J74" s="29" t="s">
-        <v>355</v>
       </c>
       <c r="K74" s="42" t="s">
         <v>16</v>
@@ -7215,56 +7377,56 @@
         <v>8</v>
       </c>
       <c r="M74" s="42" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N74" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O74" s="42" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="P74" s="42" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Q74" s="42"/>
       <c r="R74" s="42"/>
       <c r="S74" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T74" s="42" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="171">
       <c r="A75" s="28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E75" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F75" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G75" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="H75" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="I75" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="J75" s="29" t="s">
         <v>357</v>
-      </c>
-      <c r="H75" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="I75" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="J75" s="29" t="s">
-        <v>358</v>
       </c>
       <c r="K75" s="42" t="s">
         <v>16</v>
@@ -7273,56 +7435,56 @@
         <v>8</v>
       </c>
       <c r="M75" s="42" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="N75" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O75" s="42" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="P75" s="42" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Q75" s="42"/>
       <c r="R75" s="42"/>
       <c r="S75" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T75" s="42" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="57">
       <c r="A76" s="28" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B76" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E76" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G76" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="H76" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="I76" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="J76" s="29" t="s">
         <v>360</v>
-      </c>
-      <c r="H76" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="I76" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="J76" s="29" t="s">
-        <v>361</v>
       </c>
       <c r="K76" s="42" t="s">
         <v>16</v>
@@ -7331,56 +7493,56 @@
         <v>8</v>
       </c>
       <c r="M76" s="42" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="N76" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O76" s="42" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="P76" s="42" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="Q76" s="42"/>
       <c r="R76" s="42"/>
       <c r="S76" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T76" s="42" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="71.25">
       <c r="A77" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="B77" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="C77" s="29" t="s">
         <v>362</v>
       </c>
-      <c r="B77" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="C77" s="29" t="s">
+      <c r="D77" s="29" t="s">
         <v>363</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>364</v>
       </c>
       <c r="E77" s="29" t="s">
         <v>6</v>
       </c>
       <c r="F77" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="G77" s="29" t="s">
         <v>365</v>
       </c>
-      <c r="G77" s="29" t="s">
+      <c r="H77" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="H77" s="29" t="s">
+      <c r="I77" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="I77" s="29" t="s">
+      <c r="J77" s="29" t="s">
         <v>368</v>
-      </c>
-      <c r="J77" s="29" t="s">
-        <v>369</v>
       </c>
       <c r="K77" s="42" t="s">
         <v>16</v>
@@ -7389,56 +7551,56 @@
         <v>8</v>
       </c>
       <c r="M77" s="42" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="N77" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O77" s="42" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="P77" s="42" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="Q77" s="42"/>
       <c r="R77" s="42"/>
       <c r="S77" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T77" s="42" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="42.75">
       <c r="A78" s="28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B78" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C78" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="D78" s="29" t="s">
         <v>363</v>
-      </c>
-      <c r="D78" s="29" t="s">
-        <v>364</v>
       </c>
       <c r="E78" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F78" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G78" s="29" t="s">
+        <v>370</v>
+      </c>
+      <c r="H78" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="I78" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="J78" s="29" t="s">
         <v>371</v>
-      </c>
-      <c r="H78" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="I78" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="J78" s="29" t="s">
-        <v>372</v>
       </c>
       <c r="K78" s="42" t="s">
         <v>16</v>
@@ -7447,56 +7609,56 @@
         <v>8</v>
       </c>
       <c r="M78" s="42" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="N78" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O78" s="42" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="P78" s="42" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="Q78" s="42"/>
       <c r="R78" s="42"/>
       <c r="S78" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T78" s="42" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="409.5">
       <c r="A79" s="28" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C79" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="D79" s="29" t="s">
         <v>363</v>
-      </c>
-      <c r="D79" s="29" t="s">
-        <v>364</v>
       </c>
       <c r="E79" s="29" t="s">
         <v>9</v>
       </c>
       <c r="F79" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G79" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="H79" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="I79" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="J79" s="29" t="s">
         <v>374</v>
-      </c>
-      <c r="H79" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="I79" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="J79" s="29" t="s">
-        <v>375</v>
       </c>
       <c r="K79" s="42" t="s">
         <v>16</v>
@@ -7505,56 +7667,56 @@
         <v>8</v>
       </c>
       <c r="M79" s="42" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N79" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O79" s="42" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="P79" s="42" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="Q79" s="42"/>
       <c r="R79" s="42"/>
       <c r="S79" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T79" s="42" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="85.5">
       <c r="A80" s="28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B80" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="D80" s="29" t="s">
         <v>363</v>
-      </c>
-      <c r="D80" s="29" t="s">
-        <v>364</v>
       </c>
       <c r="E80" s="29" t="s">
         <v>12</v>
       </c>
       <c r="F80" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G80" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="H80" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="I80" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="J80" s="29" t="s">
         <v>377</v>
-      </c>
-      <c r="H80" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="I80" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="J80" s="29" t="s">
-        <v>378</v>
       </c>
       <c r="K80" s="42" t="s">
         <v>16</v>
@@ -7563,58 +7725,58 @@
         <v>8</v>
       </c>
       <c r="M80" s="42" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="N80" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O80" s="42" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="P80" s="42" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="Q80" s="42" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="R80" s="42"/>
       <c r="S80" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T80" s="42" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81" spans="1:20" ht="85.5">
       <c r="A81" s="30" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C81" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="D81" s="31" t="s">
         <v>363</v>
-      </c>
-      <c r="D81" s="31" t="s">
-        <v>364</v>
       </c>
       <c r="E81" s="31" t="s">
         <v>12</v>
       </c>
       <c r="F81" s="31" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G81" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="H81" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="I81" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="J81" s="31" t="s">
         <v>380</v>
-      </c>
-      <c r="H81" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="I81" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="J81" s="31" t="s">
-        <v>381</v>
       </c>
       <c r="K81" s="42" t="s">
         <v>16</v>
@@ -7623,41 +7785,41 @@
         <v>8</v>
       </c>
       <c r="M81" s="42" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="N81" s="42" t="s">
         <v>7</v>
       </c>
       <c r="O81" s="42" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="P81" s="42" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="Q81" s="42"/>
       <c r="R81" s="42"/>
       <c r="S81" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T81" s="42" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:L81">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>L2="Pass"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>L2="Fail"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>L2="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>L2="Retest"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>L2="Not Run"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7673,8 +7835,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7695,166 +7858,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18">
-      <c r="A1" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="A1" s="56" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>383</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="D3" s="33" t="s">
         <v>384</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>385</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>386</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>387</v>
       </c>
-      <c r="G3" s="33" t="s">
-        <v>388</v>
-      </c>
       <c r="H3" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="28.5">
       <c r="A4" s="35"/>
       <c r="B4" s="36" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="36" t="s">
         <v>389</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>390</v>
       </c>
       <c r="E4" s="36"/>
       <c r="F4" s="36"/>
       <c r="G4" s="36"/>
       <c r="H4" s="37" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.5">
       <c r="A5" s="35"/>
       <c r="B5" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>392</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>393</v>
       </c>
       <c r="E5" s="36"/>
       <c r="F5" s="36"/>
       <c r="G5" s="36"/>
       <c r="H5" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.5">
       <c r="A6" s="35"/>
       <c r="B6" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>395</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>396</v>
       </c>
       <c r="E6" s="36"/>
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="28.5">
       <c r="A7" s="35"/>
       <c r="B7" s="36" t="s">
+        <v>396</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="36" t="s">
         <v>397</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>398</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
       <c r="G7" s="36"/>
       <c r="H7" s="37" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.5">
       <c r="A8" s="35"/>
       <c r="B8" s="36" t="s">
+        <v>399</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>400</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="D8" s="36" t="s">
         <v>401</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>402</v>
       </c>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
       <c r="H8" s="37" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.5">
       <c r="A9" s="38"/>
       <c r="B9" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="C9" s="39" t="s">
         <v>403</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="D9" s="39" t="s">
         <v>404</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>405</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
       <c r="G9" s="39"/>
       <c r="H9" s="40" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="114">
       <c r="A10" t="s">
+        <v>563</v>
+      </c>
+      <c r="B10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>565</v>
+      </c>
+      <c r="E10" s="43" t="s">
         <v>566</v>
-      </c>
-      <c r="B10" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>401</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>568</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>569</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -7863,24 +8026,24 @@
         <v>46285</v>
       </c>
       <c r="H10" s="43" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="85.5">
       <c r="A11" t="s">
+        <v>569</v>
+      </c>
+      <c r="B11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D11" s="43" t="s">
         <v>572</v>
       </c>
-      <c r="B11" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" t="s">
-        <v>401</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>575</v>
-      </c>
       <c r="E11" s="43" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -7889,24 +8052,24 @@
         <v>46285</v>
       </c>
       <c r="H11" s="43" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="156.75">
       <c r="A12" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -7915,24 +8078,24 @@
         <v>46285</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="285">
       <c r="A13" t="s">
+        <v>584</v>
+      </c>
+      <c r="B13" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" t="s">
+        <v>400</v>
+      </c>
+      <c r="D13" s="43" t="s">
         <v>587</v>
       </c>
-      <c r="B13" t="s">
-        <v>331</v>
-      </c>
-      <c r="C13" t="s">
-        <v>401</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>590</v>
-      </c>
       <c r="E13" s="43" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -7941,7 +8104,7 @@
         <v>46285</v>
       </c>
       <c r="H13" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
